--- a/docs/testing/MMC-test-cases-ar.xlsx
+++ b/docs/testing/MMC-test-cases-ar.xlsx
@@ -13,12 +13,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="المالية وCRM" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="المشاريع والخدمة" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="المخزون والموارد البشرية" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الحسابات" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'المبيعات'!$A$1:$L$177</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'المالية وCRM'!$A$1:$L$160</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'المشاريع والخدمة'!$A$1:$L$164</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'المخزون والموارد البشرية'!$A$1:$L$174</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'الحسابات'!$A$1:$L$98</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -564,7 +566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -822,46 +824,91 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>الإجمالي</t>
-        </is>
-      </c>
-      <c r="C9" s="8">
-        <f>SUM(C5:C8)</f>
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>الحسابات</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>دفتر الأستاذ والقيود والترحيل التلقائي والضريبة والإقفال والفوترة الإلكترونية</t>
+        </is>
+      </c>
+      <c r="C9" s="5">
+        <f>COUNTA('الحسابات'!A2:A98)</f>
         <v/>
       </c>
-      <c r="D9" s="8">
-        <f>SUM(D5:D8)</f>
+      <c r="D9" s="5">
+        <f>COUNTIF('الحسابات'!G2:G98,"P1")</f>
         <v/>
       </c>
-      <c r="E9" s="8">
-        <f>SUM(E5:E8)</f>
+      <c r="E9" s="5">
+        <f>COUNTIF('الحسابات'!I2:I98,"ناجح")</f>
         <v/>
       </c>
-      <c r="F9" s="8">
-        <f>SUM(F5:F8)</f>
+      <c r="F9" s="5">
+        <f>COUNTIF('الحسابات'!I2:I98,"فاشل")</f>
         <v/>
       </c>
-      <c r="G9" s="8">
-        <f>SUM(G5:G8)</f>
+      <c r="G9" s="5">
+        <f>COUNTIF('الحسابات'!I2:I98,"محجوب")</f>
         <v/>
       </c>
-      <c r="H9" s="8">
-        <f>SUM(H5:H8)</f>
+      <c r="H9" s="5">
+        <f>COUNTIF('الحسابات'!I2:I98,"لم يُختبر")</f>
         <v/>
       </c>
-      <c r="I9" s="9">
+      <c r="I9" s="6">
         <f>IF(C9=0,0,E9/C9)</f>
         <v/>
       </c>
-      <c r="J9" s="8">
-        <f>SUM(J5:J8)</f>
+      <c r="J9" s="5">
+        <f>COUNTIFS('الحسابات'!G2:G98,"P1",'الحسابات'!I2:I98,"فاشل")</f>
         <v/>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>الإجمالي</t>
+        </is>
+      </c>
+      <c r="C10" s="8">
+        <f>SUM(C5:C9)</f>
+        <v/>
+      </c>
+      <c r="D10" s="8">
+        <f>SUM(D5:D9)</f>
+        <v/>
+      </c>
+      <c r="E10" s="8">
+        <f>SUM(E5:E9)</f>
+        <v/>
+      </c>
+      <c r="F10" s="8">
+        <f>SUM(F5:F9)</f>
+        <v/>
+      </c>
+      <c r="G10" s="8">
+        <f>SUM(G5:G9)</f>
+        <v/>
+      </c>
+      <c r="H10" s="8">
+        <f>SUM(H5:H9)</f>
+        <v/>
+      </c>
+      <c r="I10" s="9">
+        <f>IF(C10=0,0,E10/C10)</f>
+        <v/>
+      </c>
+      <c r="J10" s="8">
+        <f>SUM(J5:J9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>قاعدة الإطلاق: لا تشغيل فعلي قبل أن تكون كل حالات P1 «ناجح» (عمود «P1 فاشلة» = 0 ولا P1 «لم يُختبر»).</t>
         </is>
@@ -35387,4 +35434,5076 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L98"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="52" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>الرقم</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>الوحدة</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>السيناريو</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>الشروط المسبقة / الدور</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>الخطوات</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>النتيجة المتوقعة</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>الأولوية</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>النوع</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>الحالة</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>المختبِر</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>تاريخ الاختبار</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>ملاحظات / رقم البلاغ</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-001</t>
+        </is>
+      </c>
+      <c r="B2" s="14" t="inlineStr">
+        <is>
+          <t>دليل الحسابات</t>
+        </is>
+      </c>
+      <c r="C2" s="15" t="inlineStr">
+        <is>
+          <t>دليل الحسابات السعودي الجاهز يظهر عند أول فتح، ومن لا يملك صلاحية الدفتر لا يراه</t>
+        </is>
+      </c>
+      <c r="D2" s="14" t="inlineStr">
+        <is>
+          <t>مستأجر جديد؛ مستخدم مبيعات بلا صلاحية ledger.read ومحاسب بصلاحية ledger.read</t>
+        </is>
+      </c>
+      <c r="E2" s="14" t="inlineStr">
+        <is>
+          <t>1. بدور المحاسب افتح /accounting/accounts
+2. سجّل الدخول بدور المبيعات وحاول فتح الصفحة نفسها</t>
+        </is>
+      </c>
+      <c r="F2" s="14" t="inlineStr">
+        <is>
+          <t>يظهر الدليل هرميًا (مجموعات وحسابات: 1101 الصندوق، 1110 العملاء، 2110 ضريبة المخرجات، 4101 المبيعات…) وبأسماء عربية. المبيعات لا ترى بند «الحسابات» في القائمة ويُرفض الطلب 403</t>
+        </is>
+      </c>
+      <c r="G2" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H2" s="14" t="inlineStr">
+        <is>
+          <t>صلاحيات</t>
+        </is>
+      </c>
+      <c r="I2" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J2" s="14" t="n"/>
+      <c r="K2" s="13" t="n"/>
+      <c r="L2" s="14" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-002</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>دليل الحسابات</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>إضافة حساب تحت مجموعة من النوع نفسه برمز فريد</t>
+        </is>
+      </c>
+      <c r="D3" s="14" t="inlineStr">
+        <is>
+          <t>محاسب (ledger.write)</t>
+        </is>
+      </c>
+      <c r="E3" s="14" t="inlineStr">
+        <is>
+          <t>1. اضغط «حساب جديد»
+2. اختر مجموعة المصروفات 62 وأدخل رمزًا جديدًا واسمًا عربيًا
+3. احفظ</t>
+        </is>
+      </c>
+      <c r="F3" s="14" t="inlineStr">
+        <is>
+          <t>يُنشأ الحساب تحت المجموعة بنوع المجموعة نفسه ويظهر في الدليل وفي قوائم اختيار القيود</t>
+        </is>
+      </c>
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H3" s="14" t="inlineStr">
+        <is>
+          <t>وظيفي</t>
+        </is>
+      </c>
+      <c r="I3" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J3" s="14" t="n"/>
+      <c r="K3" s="13" t="n"/>
+      <c r="L3" s="14" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-003</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>دليل الحسابات</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>رمز حساب مكرر أو نوع لا يطابق المجموعة يُرفض</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>محاسب</t>
+        </is>
+      </c>
+      <c r="E4" s="14" t="inlineStr">
+        <is>
+          <t>1. أنشئ حسابًا برمز موجود مسبقًا
+2. أنشئ حساب إيراد تحت مجموعة مصروفات</t>
+        </is>
+      </c>
+      <c r="F4" s="14" t="inlineStr">
+        <is>
+          <t>رفض 400 برسالة واضحة في الحالتين ولا يُحفظ شيء</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H4" s="14" t="inlineStr">
+        <is>
+          <t>تحقق من المدخلات</t>
+        </is>
+      </c>
+      <c r="I4" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J4" s="14" t="n"/>
+      <c r="K4" s="13" t="n"/>
+      <c r="L4" s="14" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-004</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>دليل الحسابات</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>لا يُغيَّر رمز الحساب أو نوعه بعد استخدامه، ويُسمح بتغيير الاسم</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>حساب عليه حركات مرحّلة</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>1. افتح الحساب وعدّل الاسم العربي واحفظ
+2. حاول تغيير الرمز أو النوع</t>
+        </is>
+      </c>
+      <c r="F5" s="14" t="inlineStr">
+        <is>
+          <t>تغيير الاسم ينجح. تغيير الرمز/النوع مرفوض مع سبب (الحساب مستخدم)</t>
+        </is>
+      </c>
+      <c r="G5" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H5" s="14" t="inlineStr">
+        <is>
+          <t>حالات حدّية</t>
+        </is>
+      </c>
+      <c r="I5" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J5" s="14" t="n"/>
+      <c r="K5" s="13" t="n"/>
+      <c r="L5" s="14" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-005</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>دليل الحسابات</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>تعطيل حساب غير مستخدم وحذفه؛ الحساب المستخدم لا يُحذف</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>حساب جديد بلا حركات وآخر عليه حركات</t>
+        </is>
+      </c>
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>1. عطّل الحساب الجديد ثم احذفه
+2. حاول حذف الحساب المستخدم</t>
+        </is>
+      </c>
+      <c r="F6" s="14" t="inlineStr">
+        <is>
+          <t>الأول يُعطَّل ثم يُحذف ولا يظهر في الاختيار. الثاني مرفوض (يُعطَّل فقط) وتبقى حركاته</t>
+        </is>
+      </c>
+      <c r="G6" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H6" s="14" t="inlineStr">
+        <is>
+          <t>حالات حدّية</t>
+        </is>
+      </c>
+      <c r="I6" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J6" s="14" t="n"/>
+      <c r="K6" s="13" t="n"/>
+      <c r="L6" s="14" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-006</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>دليل الحسابات</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>تصدير الدليل إلى Excel واستيراده مع معاينة قبل التطبيق</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>محاسب</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>1. اضغط «تصدير» وافتح الملف
+2. أضف صفًّا لحساب جديد وعدّل اسم حساب في الملف
+3. ارفعه واقرأ المعاينة ثم اضغط «تطبيق»</t>
+        </is>
+      </c>
+      <c r="F7" s="14" t="inlineStr">
+        <is>
+          <t>الملف RTL بالرؤوس العربية. المعاينة تعدّد المضاف والمعدَّل والمرفوض قبل أي تغيير، والتطبيق يطبّق ما ظهر فقط</t>
+        </is>
+      </c>
+      <c r="G7" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H7" s="14" t="inlineStr">
+        <is>
+          <t>تكامل</t>
+        </is>
+      </c>
+      <c r="I7" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J7" s="14" t="n"/>
+      <c r="K7" s="13" t="n"/>
+      <c r="L7" s="14" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-007</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>الأرصدة الافتتاحية</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>الأرصدة الافتتاحية تحتاج صلاحية الإقفال (ledger.close)</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>محاسب بلا ledger.close ومالك</t>
+        </is>
+      </c>
+      <c r="E8" s="14" t="inlineStr">
+        <is>
+          <t>1. بدور المحاسب افتح /accounting/opening
+2. بدور المالك افتحها</t>
+        </is>
+      </c>
+      <c r="F8" s="14" t="inlineStr">
+        <is>
+          <t>المحاسب لا يرى البند ويُرفض إرسال القيد 403. المالك يدخل الأرصدة</t>
+        </is>
+      </c>
+      <c r="G8" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H8" s="14" t="inlineStr">
+        <is>
+          <t>صلاحيات</t>
+        </is>
+      </c>
+      <c r="I8" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J8" s="14" t="n"/>
+      <c r="K8" s="13" t="n"/>
+      <c r="L8" s="14" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-008</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>الأرصدة الافتتاحية</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>تُوازَن الأرصدة تلقائيًا مقابل «الرصيد الافتتاحي لحقوق الملكية» (3301)</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>مالك؛ تاريخ بدء التشغيل أول السنة</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>1. أدخل بنكًا 50,000 وصندوقًا 5,000 ورأس مال 40,000
+2. احفظ</t>
+        </is>
+      </c>
+      <c r="F9" s="14" t="inlineStr">
+        <is>
+          <t>يُنشأ قيد مسودة بنوع opening إجماليه 55,000، وسطر 3301 دائن 15,000 يوازن الفرق. تعطيل «موازنة تلقائية» مع فرق يُرفض 400</t>
+        </is>
+      </c>
+      <c r="G9" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H9" s="14" t="inlineStr">
+        <is>
+          <t>وظيفي</t>
+        </is>
+      </c>
+      <c r="I9" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J9" s="14" t="n"/>
+      <c r="K9" s="13" t="n"/>
+      <c r="L9" s="14" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-009</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>الأرصدة الافتتاحية</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>قيد افتتاحي حيّ واحد فقط</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>قيد افتتاحي موجود (مسودة أو مرحّل)</t>
+        </is>
+      </c>
+      <c r="E10" s="14" t="inlineStr">
+        <is>
+          <t>1. حاول إنشاء قيد افتتاحي ثانٍ</t>
+        </is>
+      </c>
+      <c r="F10" s="14" t="inlineStr">
+        <is>
+          <t>رفض 409؛ يُحرَّر القائم أو يُعكس أولًا</t>
+        </is>
+      </c>
+      <c r="G10" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H10" s="14" t="inlineStr">
+        <is>
+          <t>حالات حدّية</t>
+        </is>
+      </c>
+      <c r="I10" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J10" s="14" t="n"/>
+      <c r="K10" s="13" t="n"/>
+      <c r="L10" s="14" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-010</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>الأرصدة الافتتاحية</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>ترحيل الافتتاحي بشخص ثانٍ يحدّد تاريخ بدء التشغيل</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>قيد افتتاحي مسودة أعدّه المالك</t>
+        </is>
+      </c>
+      <c r="E11" s="14" t="inlineStr">
+        <is>
+          <t>1. بدور المحاسب (ledger.post) رحّل القيد
+2. افتح /accounting/opening وإعدادات الحسابات</t>
+        </is>
+      </c>
+      <c r="F11" s="14" t="inlineStr">
+        <is>
+          <t>يصبح posted ويظهر تاريخ البدء في الإعدادات. لا يُرحَّل شيء من المستندات المؤرخة قبله</t>
+        </is>
+      </c>
+      <c r="G11" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H11" s="14" t="inlineStr">
+        <is>
+          <t>وظيفي</t>
+        </is>
+      </c>
+      <c r="I11" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J11" s="14" t="n"/>
+      <c r="K11" s="13" t="n"/>
+      <c r="L11" s="14" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-011</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>القيود اليدوية</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>حفظ مسودة ناقصة مسموح لكن ترحيل قيد غير متوازن مرفوض</t>
+        </is>
+      </c>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>محاسب</t>
+        </is>
+      </c>
+      <c r="E12" s="14" t="inlineStr">
+        <is>
+          <t>1. أنشئ قيدًا: مصروف 120 مدين وصندوق 100 دائن واحفظ
+2. حاول ترحيله
+3. صحّح الدائن إلى 120 واحفظ</t>
+        </is>
+      </c>
+      <c r="F12" s="14" t="inlineStr">
+        <is>
+          <t>يُحفظ كمسودة برقم JV-NNNNNN. الترحيل مرفوض 400 (المدين لا يساوي الدائن). بعد التصحيح يُحفظ متوازنًا</t>
+        </is>
+      </c>
+      <c r="G12" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H12" s="14" t="inlineStr">
+        <is>
+          <t>تحقق من المدخلات</t>
+        </is>
+      </c>
+      <c r="I12" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J12" s="14" t="n"/>
+      <c r="K12" s="13" t="n"/>
+      <c r="L12" s="14" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-012</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>القيود اليدوية</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>سطور مرفوضة: مدين ودائن معًا، حساب مجموعة، أكثر من منزلتين، تاريخ قبل البدء</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>محاسب</t>
+        </is>
+      </c>
+      <c r="E13" s="14" t="inlineStr">
+        <is>
+          <t>1. جرّب كل حالة على حدة في /accounting/journal/new</t>
+        </is>
+      </c>
+      <c r="F13" s="14" t="inlineStr">
+        <is>
+          <t>كل محاولة تُرفض 400 برسالة محددة ولا يُنشأ قيد</t>
+        </is>
+      </c>
+      <c r="G13" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H13" s="14" t="inlineStr">
+        <is>
+          <t>تحقق من المدخلات</t>
+        </is>
+      </c>
+      <c r="I13" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J13" s="14" t="n"/>
+      <c r="K13" s="13" t="n"/>
+      <c r="L13" s="14" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-013</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>القيود اليدوية</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>حساب العملاء يتطلب اختيار العميل عند الترحيل</t>
+        </is>
+      </c>
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>مسودة فيها سطر على 1110 بلا عميل</t>
+        </is>
+      </c>
+      <c r="E14" s="14" t="inlineStr">
+        <is>
+          <t>1. احفظ المسودة
+2. حاول ترحيلها</t>
+        </is>
+      </c>
+      <c r="F14" s="14" t="inlineStr">
+        <is>
+          <t>تُحفظ كمسودة، ويُرفض الترحيل 400 حتى يُحدَّد العميل</t>
+        </is>
+      </c>
+      <c r="G14" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H14" s="14" t="inlineStr">
+        <is>
+          <t>تحقق من المدخلات</t>
+        </is>
+      </c>
+      <c r="I14" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J14" s="14" t="n"/>
+      <c r="K14" s="13" t="n"/>
+      <c r="L14" s="14" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-014</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>القيود اليدوية</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="inlineStr">
+        <is>
+          <t>لا يرحّل المُعِدّ قيده بنفسه (الفصل بين الإعداد والترحيل)</t>
+        </is>
+      </c>
+      <c r="D15" s="14" t="inlineStr">
+        <is>
+          <t>قيد أعدّه المحاسب</t>
+        </is>
+      </c>
+      <c r="E15" s="14" t="inlineStr">
+        <is>
+          <t>1. بدور المحاسب نفسه اضغط «ترحيل»
+2. بدور المدير العام اضغط «ترحيل»</t>
+        </is>
+      </c>
+      <c r="F15" s="14" t="inlineStr">
+        <is>
+          <t>الأول مرفوض 403. الثاني ينجح ويصبح posted مع وقت الترحيل. المالك يرحّل قيده بنفسه</t>
+        </is>
+      </c>
+      <c r="G15" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H15" s="14" t="inlineStr">
+        <is>
+          <t>صلاحيات</t>
+        </is>
+      </c>
+      <c r="I15" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J15" s="14" t="n"/>
+      <c r="K15" s="13" t="n"/>
+      <c r="L15" s="14" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-015</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>القيود اليدوية</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="inlineStr">
+        <is>
+          <t>القيد المرحَّل لا يُعدَّل ولا يُحذف</t>
+        </is>
+      </c>
+      <c r="D16" s="14" t="inlineStr">
+        <is>
+          <t>قيد مرحّل</t>
+        </is>
+      </c>
+      <c r="E16" s="14" t="inlineStr">
+        <is>
+          <t>1. حاول تعديله من الواجهة
+2. حاول حذفه
+3. حاول ترحيله مرة ثانية</t>
+        </is>
+      </c>
+      <c r="F16" s="14" t="inlineStr">
+        <is>
+          <t>الكل مرفوض 409. الزر الوحيد المتاح هو «عكس القيد»</t>
+        </is>
+      </c>
+      <c r="G16" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H16" s="14" t="inlineStr">
+        <is>
+          <t>أمان</t>
+        </is>
+      </c>
+      <c r="I16" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J16" s="14" t="n"/>
+      <c r="K16" s="13" t="n"/>
+      <c r="L16" s="14" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-016</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>القيود اليدوية</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="inlineStr">
+        <is>
+          <t>قاعدة البيانات نفسها تمنع تعديل القيد المرحّل</t>
+        </is>
+      </c>
+      <c r="D17" s="14" t="inlineStr">
+        <is>
+          <t>وصول مهندس إلى قاعدة بيانات الاختبار</t>
+        </is>
+      </c>
+      <c r="E17" s="14" t="inlineStr">
+        <is>
+          <t>1. حاول UPDATE على journal_line لقيد مرحّل
+2. حاول DELETE على journal_entry
+3. أدخل قيدًا بحالة posted مباشرة
+4. رحّل قيدًا غير متوازن مباشرة</t>
+        </is>
+      </c>
+      <c r="F17" s="14" t="inlineStr">
+        <is>
+          <t>الكل يفشل برسالة الـ trigger (immutable / cannot be deleted / must start as draft / equal debits and credits)</t>
+        </is>
+      </c>
+      <c r="G17" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H17" s="14" t="inlineStr">
+        <is>
+          <t>أمان</t>
+        </is>
+      </c>
+      <c r="I17" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J17" s="14" t="n"/>
+      <c r="K17" s="13" t="n"/>
+      <c r="L17" s="14" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-017</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>القيود اليدوية</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="inlineStr">
+        <is>
+          <t>عكس القيد: سبب إلزامي، مرة واحدة، ويربط القيدين</t>
+        </is>
+      </c>
+      <c r="D18" s="14" t="inlineStr">
+        <is>
+          <t>قيد مرحّل</t>
+        </is>
+      </c>
+      <c r="E18" s="14" t="inlineStr">
+        <is>
+          <t>1. اضغط «عكس» بلا سبب
+2. أدخل سببًا واعكس
+3. حاول عكسه ثانية وحاول عكس قيد العكس</t>
+        </is>
+      </c>
+      <c r="F18" s="14" t="inlineStr">
+        <is>
+          <t>الأول 400. الثاني ينشئ قيدًا kind=reversal مرحّلًا بنفس الإجمالي والجهات معكوسة ويظهر الرابط في القيدين. الباقي 409</t>
+        </is>
+      </c>
+      <c r="G18" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H18" s="14" t="inlineStr">
+        <is>
+          <t>وظيفي</t>
+        </is>
+      </c>
+      <c r="I18" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J18" s="14" t="n"/>
+      <c r="K18" s="13" t="n"/>
+      <c r="L18" s="14" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-018</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>القيود اليدوية</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>تصفية القيود وبحثها</t>
+        </is>
+      </c>
+      <c r="D19" s="14" t="inlineStr">
+        <is>
+          <t>عدة قيود بحالات وأنواع مختلفة</t>
+        </is>
+      </c>
+      <c r="E19" s="14" t="inlineStr">
+        <is>
+          <t>1. افتح /accounting/journal
+2. صفِّ بالحالة ثم بالنوع (يدوي/تلقائي/عكس) ثم بالفترة ثم بالنص</t>
+        </is>
+      </c>
+      <c r="F19" s="14" t="inlineStr">
+        <is>
+          <t>تتغير القائمة حسب كل مرشّح ويطابق العدد المعروض النتائج</t>
+        </is>
+      </c>
+      <c r="G19" s="13" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="H19" s="14" t="inlineStr">
+        <is>
+          <t>واجهة وعرض</t>
+        </is>
+      </c>
+      <c r="I19" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J19" s="14" t="n"/>
+      <c r="K19" s="13" t="n"/>
+      <c r="L19" s="14" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-019</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>القيود اليدوية</t>
+        </is>
+      </c>
+      <c r="C20" s="15" t="inlineStr">
+        <is>
+          <t>ترقيم القيود متسلسل بلا تكرار</t>
+        </is>
+      </c>
+      <c r="D20" s="14" t="inlineStr">
+        <is>
+          <t>محاسب</t>
+        </is>
+      </c>
+      <c r="E20" s="14" t="inlineStr">
+        <is>
+          <t>1. أنشئ ثلاثة قيود متتالية
+2. احذف مسودة الوسطى وأنشئ آخر</t>
+        </is>
+      </c>
+      <c r="F20" s="14" t="inlineStr">
+        <is>
+          <t>الأرقام JV-NNNNNN تتزايد ولا يُعاد استخدام رقم محذوف</t>
+        </is>
+      </c>
+      <c r="G20" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H20" s="14" t="inlineStr">
+        <is>
+          <t>حالات حدّية</t>
+        </is>
+      </c>
+      <c r="I20" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J20" s="14" t="n"/>
+      <c r="K20" s="13" t="n"/>
+      <c r="L20" s="14" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-020</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>الفترات والإعدادات</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>تقفل الفترة: لا ترحيل ولا إنشاء ولا عكس داخلها</t>
+        </is>
+      </c>
+      <c r="D21" s="14" t="inlineStr">
+        <is>
+          <t>مدير عام؛ مسودة بتاريخ أمس</t>
+        </is>
+      </c>
+      <c r="E21" s="14" t="inlineStr">
+        <is>
+          <t>1. افتح الإعدادات واقفل الفترة حتى أمس
+2. حاول ترحيل المسودة
+3. حاول إنشاء قيد بتاريخ داخل الفترة
+4. حاول عكس قيد قديم بتاريخ داخل الفترة
+5. أنشئ قيدًا بتاريخ اليوم</t>
+        </is>
+      </c>
+      <c r="F21" s="14" t="inlineStr">
+        <is>
+          <t>الثلاثة الأولى مرفوضة 400 والأخير ينجح. يعرض الإقفال عدد المسودات داخل الفترة</t>
+        </is>
+      </c>
+      <c r="G21" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H21" s="14" t="inlineStr">
+        <is>
+          <t>وظيفي</t>
+        </is>
+      </c>
+      <c r="I21" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J21" s="14" t="n"/>
+      <c r="K21" s="13" t="n"/>
+      <c r="L21" s="14" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-021</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>الفترات والإعدادات</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>من يقفل الفترة ومن يفتحها</t>
+        </is>
+      </c>
+      <c r="D22" s="14" t="inlineStr">
+        <is>
+          <t>محاسب ومدير عام ومالك</t>
+        </is>
+      </c>
+      <c r="E22" s="14" t="inlineStr">
+        <is>
+          <t>1. المحاسب يحاول القفل
+2. المدير يقفل حتى تاريخ مستقبلي ثم حتى أمس
+3. المدير يحاول الفتح
+4. المالك يفتح بسبب</t>
+        </is>
+      </c>
+      <c r="F22" s="14" t="inlineStr">
+        <is>
+          <t>المحاسب 403. المستقبلي 400. المدير يقفل أمس بنجاح. الفتح للمالك فقط مع سبب إلزامي ويُسجَّل في سجل التدقيق</t>
+        </is>
+      </c>
+      <c r="G22" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H22" s="14" t="inlineStr">
+        <is>
+          <t>صلاحيات</t>
+        </is>
+      </c>
+      <c r="I22" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J22" s="14" t="n"/>
+      <c r="K22" s="13" t="n"/>
+      <c r="L22" s="14" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-022</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>الفترات والإعدادات</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="inlineStr">
+        <is>
+          <t>تقويم السنة المالية لا يتغير بعد وجود قيود مرحّلة</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="inlineStr">
+        <is>
+          <t>قيود مرحّلة موجودة</t>
+        </is>
+      </c>
+      <c r="E23" s="14" t="inlineStr">
+        <is>
+          <t>1. افتح إعدادات الحسابات وغيّر شهر بداية السنة المالية</t>
+        </is>
+      </c>
+      <c r="F23" s="14" t="inlineStr">
+        <is>
+          <t>المحاسب 403 والمالك 409 (توجد قيود مرحّلة). تغيير سياسة WIP أو نسبة GOSI لصاحب العمل مسموح</t>
+        </is>
+      </c>
+      <c r="G23" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H23" s="14" t="inlineStr">
+        <is>
+          <t>حالات حدّية</t>
+        </is>
+      </c>
+      <c r="I23" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J23" s="14" t="n"/>
+      <c r="K23" s="13" t="n"/>
+      <c r="L23" s="14" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-023</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t>الفترات والإعدادات</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>أسماء حسابات الطرق (نقد، مدى، تحويل…) تأتي من الإعدادات</t>
+        </is>
+      </c>
+      <c r="D24" s="14" t="inlineStr">
+        <is>
+          <t>إعدادات افتراضية</t>
+        </is>
+      </c>
+      <c r="E24" s="14" t="inlineStr">
+        <is>
+          <t>1. افتح الإعدادات وراجع حساب كل طريقة دفع
+2. اجعل الحساب البنكي الافتراضي مجموعة</t>
+        </is>
+      </c>
+      <c r="F24" s="14" t="inlineStr">
+        <is>
+          <t>نقد=1101 ومدى=1104 افتراضيًا، واختيار مجموعة كحساب افتراضي مرفوض 400</t>
+        </is>
+      </c>
+      <c r="G24" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H24" s="14" t="inlineStr">
+        <is>
+          <t>تحقق من المدخلات</t>
+        </is>
+      </c>
+      <c r="I24" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J24" s="14" t="n"/>
+      <c r="K24" s="13" t="n"/>
+      <c r="L24" s="14" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-024</t>
+        </is>
+      </c>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>الفترات والإعدادات</t>
+        </is>
+      </c>
+      <c r="C25" s="15" t="inlineStr">
+        <is>
+          <t>سجل التدقيق يحفظ إجراءات الدفتر</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="inlineStr">
+        <is>
+          <t>مالك</t>
+        </is>
+      </c>
+      <c r="E25" s="14" t="inlineStr">
+        <is>
+          <t>1. رحّل قيدًا واعكسه واقفل فترة
+2. افتح سجل التدقيق</t>
+        </is>
+      </c>
+      <c r="F25" s="14" t="inlineStr">
+        <is>
+          <t>تظهر journal_entry:post و reverse وقفل الفترة بمن نفّذها ومتى (سلسلة هاش لا تُعدَّل)</t>
+        </is>
+      </c>
+      <c r="G25" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H25" s="14" t="inlineStr">
+        <is>
+          <t>أمان</t>
+        </is>
+      </c>
+      <c r="I25" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J25" s="14" t="n"/>
+      <c r="K25" s="13" t="n"/>
+      <c r="L25" s="14" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-025</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t>التقارير المالية</t>
+        </is>
+      </c>
+      <c r="C26" s="15" t="inlineStr">
+        <is>
+          <t>ميزان المراجعة متوازن وبه مجاميع المجموعات</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>عدة قيود مرحّلة</t>
+        </is>
+      </c>
+      <c r="E26" s="14" t="inlineStr">
+        <is>
+          <t>1. افتح /accounting/reports تبويب ميزان المراجعة
+2. غيّر المستوى وفعّل «إخفاء الأصفار»</t>
+        </is>
+      </c>
+      <c r="F26" s="14" t="inlineStr">
+        <is>
+          <t>إجمالي المدين = الدائن، والمجموعات تجمع أبناءها، والتصفية لا تغيّر الإجماليات</t>
+        </is>
+      </c>
+      <c r="G26" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H26" s="14" t="inlineStr">
+        <is>
+          <t>وظيفي</t>
+        </is>
+      </c>
+      <c r="I26" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J26" s="14" t="n"/>
+      <c r="K26" s="13" t="n"/>
+      <c r="L26" s="14" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-026</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>التقارير المالية</t>
+        </is>
+      </c>
+      <c r="C27" s="15" t="inlineStr">
+        <is>
+          <t>كشف حساب برصيد متحرك ويُصفّى بالعميل</t>
+        </is>
+      </c>
+      <c r="D27" s="14" t="inlineStr">
+        <is>
+          <t>حساب العملاء عليه حركات لعميلين</t>
+        </is>
+      </c>
+      <c r="E27" s="14" t="inlineStr">
+        <is>
+          <t>1. افتح كشف الحساب لـ 1110
+2. صفِّ بعميل واحد</t>
+        </is>
+      </c>
+      <c r="F27" s="14" t="inlineStr">
+        <is>
+          <t>الرصيد الجاري يتراكم سطرًا بسطر والرصيد الختامي = مجموع الحركات، وبعد التصفية يخص العميل وحده</t>
+        </is>
+      </c>
+      <c r="G27" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H27" s="14" t="inlineStr">
+        <is>
+          <t>وظيفي</t>
+        </is>
+      </c>
+      <c r="I27" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J27" s="14" t="n"/>
+      <c r="K27" s="13" t="n"/>
+      <c r="L27" s="14" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-027</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>التقارير المالية</t>
+        </is>
+      </c>
+      <c r="C28" s="15" t="inlineStr">
+        <is>
+          <t>قائمة الدخل والميزانية متفقتان على الربح</t>
+        </is>
+      </c>
+      <c r="D28" s="14" t="inlineStr">
+        <is>
+          <t>إيرادات ومصروفات في السنة</t>
+        </is>
+      </c>
+      <c r="E28" s="14" t="inlineStr">
+        <is>
+          <t>1. افتح قائمة الدخل للسنة
+2. افتح الميزانية في آخر السنة</t>
+        </is>
+      </c>
+      <c r="F28" s="14" t="inlineStr">
+        <is>
+          <t>صافي الربح في قائمة الدخل = ربح السنة في حقوق الملكية بالميزانية، والميزانية متوازنة (الأصول = الخصوم + حقوق الملكية)</t>
+        </is>
+      </c>
+      <c r="G28" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H28" s="14" t="inlineStr">
+        <is>
+          <t>وظيفي</t>
+        </is>
+      </c>
+      <c r="I28" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J28" s="14" t="n"/>
+      <c r="K28" s="13" t="n"/>
+      <c r="L28" s="14" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-028</t>
+        </is>
+      </c>
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>التقارير المالية</t>
+        </is>
+      </c>
+      <c r="C29" s="15" t="inlineStr">
+        <is>
+          <t>دفتر اليومية يعرض القيود بسطورها</t>
+        </is>
+      </c>
+      <c r="D29" s="14" t="inlineStr">
+        <is>
+          <t>قيود في الفترة</t>
+        </is>
+      </c>
+      <c r="E29" s="14" t="inlineStr">
+        <is>
+          <t>1. افتح تبويب دفتر اليومية وحدّد فترة</t>
+        </is>
+      </c>
+      <c r="F29" s="14" t="inlineStr">
+        <is>
+          <t>كل قيد بسطوره ومجموعه وبترتيب التاريخ والرقم</t>
+        </is>
+      </c>
+      <c r="G29" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H29" s="14" t="inlineStr">
+        <is>
+          <t>واجهة وعرض</t>
+        </is>
+      </c>
+      <c r="I29" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J29" s="14" t="n"/>
+      <c r="K29" s="13" t="n"/>
+      <c r="L29" s="14" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-029</t>
+        </is>
+      </c>
+      <c r="B30" s="14" t="inlineStr">
+        <is>
+          <t>التقارير المالية</t>
+        </is>
+      </c>
+      <c r="C30" s="15" t="inlineStr">
+        <is>
+          <t>تصدير كل تقرير إلى Excel وPDF</t>
+        </is>
+      </c>
+      <c r="D30" s="14" t="inlineStr">
+        <is>
+          <t>خدمة Gotenberg تعمل لـ PDF</t>
+        </is>
+      </c>
+      <c r="E30" s="14" t="inlineStr">
+        <is>
+          <t>1. من كل تبويب اضغط Excel ثم PDF
+2. افتح الملفين</t>
+        </is>
+      </c>
+      <c r="F30" s="14" t="inlineStr">
+        <is>
+          <t>Excel بورقة RTL ورأس مجمّد وأرقام تُقرأ كأرقام. PDF عربي من اليمين لليسار. القيم مطابقة للشاشة</t>
+        </is>
+      </c>
+      <c r="G30" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H30" s="14" t="inlineStr">
+        <is>
+          <t>واجهة وعرض</t>
+        </is>
+      </c>
+      <c r="I30" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J30" s="14" t="n"/>
+      <c r="K30" s="13" t="n"/>
+      <c r="L30" s="14" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-030</t>
+        </is>
+      </c>
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>التقارير المالية</t>
+        </is>
+      </c>
+      <c r="C31" s="15" t="inlineStr">
+        <is>
+          <t>لوحة الحسابات تعرض النقد والذمم والربح وفحوص السلامة</t>
+        </is>
+      </c>
+      <c r="D31" s="14" t="inlineStr">
+        <is>
+          <t>قيود مرحّلة</t>
+        </is>
+      </c>
+      <c r="E31" s="14" t="inlineStr">
+        <is>
+          <t>1. افتح /accounting</t>
+        </is>
+      </c>
+      <c r="F31" s="14" t="inlineStr">
+        <is>
+          <t>بطاقات النقد والذمم المدينة والدائنة وربح الفترة، وقائمة فحوص التسوية (ميزان المراجعة، الانتظار، ضريبة…) بحالة سليمة/تحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="G31" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H31" s="14" t="inlineStr">
+        <is>
+          <t>واجهة وعرض</t>
+        </is>
+      </c>
+      <c r="I31" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J31" s="14" t="n"/>
+      <c r="K31" s="13" t="n"/>
+      <c r="L31" s="14" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-031</t>
+        </is>
+      </c>
+      <c r="B32" s="14" t="inlineStr">
+        <is>
+          <t>الترحيل التلقائي</t>
+        </is>
+      </c>
+      <c r="C32" s="15" t="inlineStr">
+        <is>
+          <t>لا يُرحَّل أي مستند مؤرخ قبل تاريخ بدء التشغيل</t>
+        </is>
+      </c>
+      <c r="D32" s="14" t="inlineStr">
+        <is>
+          <t>تاريخ البدء محدد؛ فاتورة قديمة قبله</t>
+        </is>
+      </c>
+      <c r="E32" s="14" t="inlineStr">
+        <is>
+          <t>1. شغّل «ترحيل الآن» من /accounting/exceptions أو انتظر المهمة</t>
+        </is>
+      </c>
+      <c r="F32" s="14" t="inlineStr">
+        <is>
+          <t>المستند القديم يُتخطّى ولا يظهر كخطأ ولا يغيّر أي رصيد</t>
+        </is>
+      </c>
+      <c r="G32" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H32" s="14" t="inlineStr">
+        <is>
+          <t>حالات حدّية</t>
+        </is>
+      </c>
+      <c r="I32" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J32" s="14" t="n"/>
+      <c r="K32" s="13" t="n"/>
+      <c r="L32" s="14" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-032</t>
+        </is>
+      </c>
+      <c r="B33" s="14" t="inlineStr">
+        <is>
+          <t>الترحيل التلقائي</t>
+        </is>
+      </c>
+      <c r="C33" s="15" t="inlineStr">
+        <is>
+          <t>عقد بضريبة: 386 ثم 386 ثم 388 تُرحَّل كلها وتصفّر العميل</t>
+        </is>
+      </c>
+      <c r="D33" s="14" t="inlineStr">
+        <is>
+          <t>عقد 11,500 بضريبة 15% بدفعتين مقدمتين وفاتورة نهائية</t>
+        </is>
+      </c>
+      <c r="E33" s="14" t="inlineStr">
+        <is>
+          <t>1. وقّع العقد واطلب الدفعة الأولى والثانية واستلمهما
+2. اطلب الدفعة الأخيرة
+3. افتح كشف 1110 و2102 للعميل</t>
+        </is>
+      </c>
+      <c r="F33" s="14" t="inlineStr">
+        <is>
+          <t>386: مدين العملاء 5,750 دائن دفعات مقدمة 5,000 وضريبة مخرجات 750 بكود S. 388: إيراد 10,000 ودفعات مقدمة تُقفَل في القيد نفسه وضريبة 150 المتبقية. يصفّر رصيد العميل في 1110 و2102</t>
+        </is>
+      </c>
+      <c r="G33" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H33" s="14" t="inlineStr">
+        <is>
+          <t>تكامل</t>
+        </is>
+      </c>
+      <c r="I33" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J33" s="14" t="n"/>
+      <c r="K33" s="13" t="n"/>
+      <c r="L33" s="14" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-033</t>
+        </is>
+      </c>
+      <c r="B34" s="14" t="inlineStr">
+        <is>
+          <t>الترحيل التلقائي</t>
+        </is>
+      </c>
+      <c r="C34" s="15" t="inlineStr">
+        <is>
+          <t>دفعات العملاء تُرحَّل على حساب الطريقة</t>
+        </is>
+      </c>
+      <c r="D34" s="14" t="inlineStr">
+        <is>
+          <t>دفعات بطرق: نقد، مدى، تحويل</t>
+        </is>
+      </c>
+      <c r="E34" s="14" t="inlineStr">
+        <is>
+          <t>1. سجّل دفعة بكل طريقة
+2. افتح قيود الدفعات</t>
+        </is>
+      </c>
+      <c r="F34" s="14" t="inlineStr">
+        <is>
+          <t>مدين حساب الطريقة (1101 نقد، 1104 مدى، 1103 بنك) ودائن العملاء 1110 بجهة العميل</t>
+        </is>
+      </c>
+      <c r="G34" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H34" s="14" t="inlineStr">
+        <is>
+          <t>تكامل</t>
+        </is>
+      </c>
+      <c r="I34" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J34" s="14" t="n"/>
+      <c r="K34" s="13" t="n"/>
+      <c r="L34" s="14" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-034</t>
+        </is>
+      </c>
+      <c r="B35" s="14" t="inlineStr">
+        <is>
+          <t>الترحيل التلقائي</t>
+        </is>
+      </c>
+      <c r="C35" s="15" t="inlineStr">
+        <is>
+          <t>تشغيل المحرك مرة ثانية لا يُنشئ شيئًا</t>
+        </is>
+      </c>
+      <c r="D35" s="14" t="inlineStr">
+        <is>
+          <t>مستندات مرحّلة</t>
+        </is>
+      </c>
+      <c r="E35" s="14" t="inlineStr">
+        <is>
+          <t>1. اضغط «ترحيل الآن» مرتين متتاليتين
+2. قارن عدد القيود</t>
+        </is>
+      </c>
+      <c r="F35" s="14" t="inlineStr">
+        <is>
+          <t>العدد ثابت (تُرحَّل كل مصدر مرة واحدة)، ولا تظهر أخطاء مكررة</t>
+        </is>
+      </c>
+      <c r="G35" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H35" s="14" t="inlineStr">
+        <is>
+          <t>حالات حدّية</t>
+        </is>
+      </c>
+      <c r="I35" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J35" s="14" t="n"/>
+      <c r="K35" s="13" t="n"/>
+      <c r="L35" s="14" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-035</t>
+        </is>
+      </c>
+      <c r="B36" s="14" t="inlineStr">
+        <is>
+          <t>الترحيل التلقائي</t>
+        </is>
+      </c>
+      <c r="C36" s="15" t="inlineStr">
+        <is>
+          <t>إشعار دائن 381 يُرحَّل عكس البيع</t>
+        </is>
+      </c>
+      <c r="D36" s="14" t="inlineStr">
+        <is>
+          <t>فاتورة مرحّلة وإشعار دائن عليها بسبب</t>
+        </is>
+      </c>
+      <c r="E36" s="14" t="inlineStr">
+        <is>
+          <t>1. أصدر إشعارًا دائنًا من صفحة الفاتورة
+2. افتح قيده</t>
+        </is>
+      </c>
+      <c r="F36" s="14" t="inlineStr">
+        <is>
+          <t>قيد تلقائي يعكس الإيراد والضريبة والعملاء بالمبالغ الموجبة نفسها، ومرتبط بالفاتورة الأصلية</t>
+        </is>
+      </c>
+      <c r="G36" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H36" s="14" t="inlineStr">
+        <is>
+          <t>وظيفي</t>
+        </is>
+      </c>
+      <c r="I36" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J36" s="14" t="n"/>
+      <c r="K36" s="13" t="n"/>
+      <c r="L36" s="14" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-036</t>
+        </is>
+      </c>
+      <c r="B37" s="14" t="inlineStr">
+        <is>
+          <t>الترحيل التلقائي</t>
+        </is>
+      </c>
+      <c r="C37" s="15" t="inlineStr">
+        <is>
+          <t>إلغاء فاتورة في النظام الخلفي يعكسها مرة واحدة</t>
+        </is>
+      </c>
+      <c r="D37" s="14" t="inlineStr">
+        <is>
+          <t>فاتورة مرحّلة</t>
+        </is>
+      </c>
+      <c r="E37" s="14" t="inlineStr">
+        <is>
+          <t>1. ألغِ الفاتورة (حالة cancelled)
+2. شغّل الترحيل مرتين</t>
+        </is>
+      </c>
+      <c r="F37" s="14" t="inlineStr">
+        <is>
+          <t>قيد عكس واحد فقط مرتبط بالأصل (source_event يبدأ بـ cancel:) وصافي الإيراد صفر</t>
+        </is>
+      </c>
+      <c r="G37" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H37" s="14" t="inlineStr">
+        <is>
+          <t>حالات حدّية</t>
+        </is>
+      </c>
+      <c r="I37" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J37" s="14" t="n"/>
+      <c r="K37" s="13" t="n"/>
+      <c r="L37" s="14" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-037</t>
+        </is>
+      </c>
+      <c r="B38" s="14" t="inlineStr">
+        <is>
+          <t>الترحيل التلقائي</t>
+        </is>
+      </c>
+      <c r="C38" s="15" t="inlineStr">
+        <is>
+          <t>تغيّر مبلغ فاتورة بعد ترحيلها يُعلَّم ولا يُعاد ترحيله</t>
+        </is>
+      </c>
+      <c r="D38" s="14" t="inlineStr">
+        <is>
+          <t>فاتورة مرحّلة؛ تعديل مبلغها مباشرة</t>
+        </is>
+      </c>
+      <c r="E38" s="14" t="inlineStr">
+        <is>
+          <t>1. شغّل الترحيل
+2. افتح بنود «تغيّر بعد الترحيل» في شاشة الانتظار</t>
+        </is>
+      </c>
+      <c r="F38" s="14" t="inlineStr">
+        <is>
+          <t>تظهر الفاتورة في القائمة ويبقى قيدها الأصلي وحده؛ التصحيح يتم بعكس وإعادة إصدار</t>
+        </is>
+      </c>
+      <c r="G38" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H38" s="14" t="inlineStr">
+        <is>
+          <t>حالات حدّية</t>
+        </is>
+      </c>
+      <c r="I38" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J38" s="14" t="n"/>
+      <c r="K38" s="13" t="n"/>
+      <c r="L38" s="14" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-038</t>
+        </is>
+      </c>
+      <c r="B39" s="14" t="inlineStr">
+        <is>
+          <t>الترحيل التلقائي</t>
+        </is>
+      </c>
+      <c r="C39" s="15" t="inlineStr">
+        <is>
+          <t>سند صرف معتمد يُرحَّل على الحساب المقابل مقابل الصندوق</t>
+        </is>
+      </c>
+      <c r="D39" s="14" t="inlineStr">
+        <is>
+          <t>سند صرف بحساب 6207 وتكلفة مركز</t>
+        </is>
+      </c>
+      <c r="E39" s="14" t="inlineStr">
+        <is>
+          <t>1. أنشئ السند واعتمده بشخص آخر
+2. افتح القيد</t>
+        </is>
+      </c>
+      <c r="F39" s="14" t="inlineStr">
+        <is>
+          <t>مسودة السند لا تُرحَّل. بعد الاعتماد: مدين 6207 دائن 1101 ويحمل مركز التكلفة/المشروع</t>
+        </is>
+      </c>
+      <c r="G39" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H39" s="14" t="inlineStr">
+        <is>
+          <t>تكامل</t>
+        </is>
+      </c>
+      <c r="I39" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J39" s="14" t="n"/>
+      <c r="K39" s="13" t="n"/>
+      <c r="L39" s="14" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-039</t>
+        </is>
+      </c>
+      <c r="B40" s="14" t="inlineStr">
+        <is>
+          <t>الترحيل التلقائي</t>
+        </is>
+      </c>
+      <c r="C40" s="15" t="inlineStr">
+        <is>
+          <t>حساب مقابل يتطلب طرفًا بلا طرف، أو حساب مجموعة، يُرفض</t>
+        </is>
+      </c>
+      <c r="D40" s="14" t="inlineStr">
+        <is>
+          <t>محاسب</t>
+        </is>
+      </c>
+      <c r="E40" s="14" t="inlineStr">
+        <is>
+          <t>1. أنشئ سند صرف بحساب 1110 دون عميل
+2. أنشئ آخر بحساب مجموعة</t>
+        </is>
+      </c>
+      <c r="F40" s="14" t="inlineStr">
+        <is>
+          <t>رفض 400 في الحالتين</t>
+        </is>
+      </c>
+      <c r="G40" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H40" s="14" t="inlineStr">
+        <is>
+          <t>تحقق من المدخلات</t>
+        </is>
+      </c>
+      <c r="I40" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J40" s="14" t="n"/>
+      <c r="K40" s="13" t="n"/>
+      <c r="L40" s="14" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-040</t>
+        </is>
+      </c>
+      <c r="B41" s="14" t="inlineStr">
+        <is>
+          <t>الترحيل التلقائي</t>
+        </is>
+      </c>
+      <c r="C41" s="15" t="inlineStr">
+        <is>
+          <t>إلغاء سند معتمد يعكس قيده مرة واحدة</t>
+        </is>
+      </c>
+      <c r="D41" s="14" t="inlineStr">
+        <is>
+          <t>سند معتمد مرحّل</t>
+        </is>
+      </c>
+      <c r="E41" s="14" t="inlineStr">
+        <is>
+          <t>1. ألغِ السند بسبب
+2. شغّل الترحيل</t>
+        </is>
+      </c>
+      <c r="F41" s="14" t="inlineStr">
+        <is>
+          <t>قيدان فقط: أصلي وعكس، وصافي المصروف صفر</t>
+        </is>
+      </c>
+      <c r="G41" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H41" s="14" t="inlineStr">
+        <is>
+          <t>حالات حدّية</t>
+        </is>
+      </c>
+      <c r="I41" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J41" s="14" t="n"/>
+      <c r="K41" s="13" t="n"/>
+      <c r="L41" s="14" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-041</t>
+        </is>
+      </c>
+      <c r="B42" s="14" t="inlineStr">
+        <is>
+          <t>الترحيل التلقائي</t>
+        </is>
+      </c>
+      <c r="C42" s="15" t="inlineStr">
+        <is>
+          <t>سند قبض من عميل يخفض رصيد ذمته</t>
+        </is>
+      </c>
+      <c r="D42" s="14" t="inlineStr">
+        <is>
+          <t>عميل رصيده 1110 موجب</t>
+        </is>
+      </c>
+      <c r="E42" s="14" t="inlineStr">
+        <is>
+          <t>1. أنشئ سند قبض 500 تحويل واعتمده
+2. افتح كشف العميل</t>
+        </is>
+      </c>
+      <c r="F42" s="14" t="inlineStr">
+        <is>
+          <t>مدين 1103 البنك 500 ودائن 1110 للعميل 500؛ يقل رصيده 500</t>
+        </is>
+      </c>
+      <c r="G42" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H42" s="14" t="inlineStr">
+        <is>
+          <t>تكامل</t>
+        </is>
+      </c>
+      <c r="I42" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J42" s="14" t="n"/>
+      <c r="K42" s="13" t="n"/>
+      <c r="L42" s="14" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-042</t>
+        </is>
+      </c>
+      <c r="B43" s="14" t="inlineStr">
+        <is>
+          <t>الترحيل التلقائي</t>
+        </is>
+      </c>
+      <c r="C43" s="15" t="inlineStr">
+        <is>
+          <t>سند غير مصنّف يذهب إلى حساب الانتظار 9101 ويظهر في الاستثناءات</t>
+        </is>
+      </c>
+      <c r="D43" s="14" t="inlineStr">
+        <is>
+          <t>سند صرف بلا حساب مقابل</t>
+        </is>
+      </c>
+      <c r="E43" s="14" t="inlineStr">
+        <is>
+          <t>1. اعتمد السند
+2. افتح /accounting/exceptions
+3. افتح فحوص التسوية</t>
+        </is>
+      </c>
+      <c r="F43" s="14" t="inlineStr">
+        <is>
+          <t>السطر على 9101 ويظهر بالمبلغ والجهة وزر «إعادة تصنيف». فحص «الانتظار» غير سليم وفحص ميزان المراجعة سليم</t>
+        </is>
+      </c>
+      <c r="G43" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H43" s="14" t="inlineStr">
+        <is>
+          <t>وظيفي</t>
+        </is>
+      </c>
+      <c r="I43" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J43" s="14" t="n"/>
+      <c r="K43" s="13" t="n"/>
+      <c r="L43" s="14" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-043</t>
+        </is>
+      </c>
+      <c r="B44" s="14" t="inlineStr">
+        <is>
+          <t>الترحيل التلقائي</t>
+        </is>
+      </c>
+      <c r="C44" s="15" t="inlineStr">
+        <is>
+          <t>إعادة التصنيف تعكس القيد وتُنشئ آخر ويربط بينهما</t>
+        </is>
+      </c>
+      <c r="D44" s="14" t="inlineStr">
+        <is>
+          <t>بند في 9101</t>
+        </is>
+      </c>
+      <c r="E44" s="14" t="inlineStr">
+        <is>
+          <t>1. اختر 6207 كحساب صحيح واضغط «تصنيف»
+2. كرّر العملية على البند نفسه</t>
+        </is>
+      </c>
+      <c r="F44" s="14" t="inlineStr">
+        <is>
+          <t>يُنشأ عكس وقيد جديد على 6207 ويختفي البند من الانتظار. التكرار 409. الإلغاء لاحقًا يعكس القيد الحيّ مرة واحدة</t>
+        </is>
+      </c>
+      <c r="G44" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H44" s="14" t="inlineStr">
+        <is>
+          <t>وظيفي</t>
+        </is>
+      </c>
+      <c r="I44" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J44" s="14" t="n"/>
+      <c r="K44" s="13" t="n"/>
+      <c r="L44" s="14" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-044</t>
+        </is>
+      </c>
+      <c r="B45" s="14" t="inlineStr">
+        <is>
+          <t>الترحيل التلقائي</t>
+        </is>
+      </c>
+      <c r="C45" s="15" t="inlineStr">
+        <is>
+          <t>مستند بتاريخ داخل فترة مقفلة يُرحَّل في أول يوم مفتوح</t>
+        </is>
+      </c>
+      <c r="D45" s="14" t="inlineStr">
+        <is>
+          <t>فترة مقفلة حتى أمس ومستند بتاريخ سابق</t>
+        </is>
+      </c>
+      <c r="E45" s="14" t="inlineStr">
+        <is>
+          <t>1. شغّل الترحيل</t>
+        </is>
+      </c>
+      <c r="F45" s="14" t="inlineStr">
+        <is>
+          <t>يُرحَّل بتاريخ أول يوم مفتوح مع ملاحظة بالتاريخ الأصلي؛ لا يخرج رصيد الفترة المقفلة عن توازنه</t>
+        </is>
+      </c>
+      <c r="G45" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H45" s="14" t="inlineStr">
+        <is>
+          <t>حالات حدّية</t>
+        </is>
+      </c>
+      <c r="I45" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J45" s="14" t="n"/>
+      <c r="K45" s="13" t="n"/>
+      <c r="L45" s="14" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-045</t>
+        </is>
+      </c>
+      <c r="B46" s="14" t="inlineStr">
+        <is>
+          <t>الترحيل التلقائي</t>
+        </is>
+      </c>
+      <c r="C46" s="15" t="inlineStr">
+        <is>
+          <t>استلام بضاعة يُرحَّل مخزونًا مقابل GRNI</t>
+        </is>
+      </c>
+      <c r="D46" s="14" t="inlineStr">
+        <is>
+          <t>أمر شراء ومستلم بتكلفة 20 للوحدة</t>
+        </is>
+      </c>
+      <c r="E46" s="14" t="inlineStr">
+        <is>
+          <t>1. اعتمد أمر الشراء وسجّل الاستلام
+2. افتح القيد</t>
+        </is>
+      </c>
+      <c r="F46" s="14" t="inlineStr">
+        <is>
+          <t>مدين المخزون 1130 ودائن البضاعة المستلمة غير المفوترة 2103 بتكلفة الاستلام</t>
+        </is>
+      </c>
+      <c r="G46" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H46" s="14" t="inlineStr">
+        <is>
+          <t>تكامل</t>
+        </is>
+      </c>
+      <c r="I46" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J46" s="14" t="n"/>
+      <c r="K46" s="13" t="n"/>
+      <c r="L46" s="14" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-046</t>
+        </is>
+      </c>
+      <c r="B47" s="14" t="inlineStr">
+        <is>
+          <t>الترحيل التلقائي</t>
+        </is>
+      </c>
+      <c r="C47" s="15" t="inlineStr">
+        <is>
+          <t>فاتورة المورد: تُقفل GRNI، فرق السعر، ضريبة المدخلات، والدائن للمورد</t>
+        </is>
+      </c>
+      <c r="D47" s="14" t="inlineStr">
+        <is>
+          <t>استلام 200 وفاتورة مورد 210 بضريبة 15%</t>
+        </is>
+      </c>
+      <c r="E47" s="14" t="inlineStr">
+        <is>
+          <t>1. أدخل فاتورة المورد واعتمدها
+2. افتح قيدها</t>
+        </is>
+      </c>
+      <c r="F47" s="14" t="inlineStr">
+        <is>
+          <t>مدين 2103 بـ 200، مدين 5105 فرق سعر 10، مدين 1140 ضريبة 31.50، دائن 2101 المورد 241.50</t>
+        </is>
+      </c>
+      <c r="G47" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H47" s="14" t="inlineStr">
+        <is>
+          <t>تكامل</t>
+        </is>
+      </c>
+      <c r="I47" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J47" s="14" t="n"/>
+      <c r="K47" s="13" t="n"/>
+      <c r="L47" s="14" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-047</t>
+        </is>
+      </c>
+      <c r="B48" s="14" t="inlineStr">
+        <is>
+          <t>الترحيل التلقائي</t>
+        </is>
+      </c>
+      <c r="C48" s="15" t="inlineStr">
+        <is>
+          <t>دفع المورد يُرحَّل مرة، وإبطاله يعكسه</t>
+        </is>
+      </c>
+      <c r="D48" s="14" t="inlineStr">
+        <is>
+          <t>فاتورة مورد معتمدة</t>
+        </is>
+      </c>
+      <c r="E48" s="14" t="inlineStr">
+        <is>
+          <t>1. سجّل دفعة 100 بنكية
+2. أبطلها</t>
+        </is>
+      </c>
+      <c r="F48" s="14" t="inlineStr">
+        <is>
+          <t>مدين 2101 دائن 1103 ثم عكس عند الإبطال وعودة الرصيد للأصل</t>
+        </is>
+      </c>
+      <c r="G48" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H48" s="14" t="inlineStr">
+        <is>
+          <t>تكامل</t>
+        </is>
+      </c>
+      <c r="I48" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J48" s="14" t="n"/>
+      <c r="K48" s="13" t="n"/>
+      <c r="L48" s="14" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-048</t>
+        </is>
+      </c>
+      <c r="B49" s="14" t="inlineStr">
+        <is>
+          <t>الترحيل التلقائي</t>
+        </is>
+      </c>
+      <c r="C49" s="15" t="inlineStr">
+        <is>
+          <t>إلغاء فاتورة مورد غير مدفوعة يعكس مرة واحدة والمدفوعة تُرفض</t>
+        </is>
+      </c>
+      <c r="D49" s="14" t="inlineStr">
+        <is>
+          <t>فاتورة مورد غير مدفوعة وأخرى مدفوعة</t>
+        </is>
+      </c>
+      <c r="E49" s="14" t="inlineStr">
+        <is>
+          <t>1. ألغِ الأولى
+2. حاول إلغاء الثانية</t>
+        </is>
+      </c>
+      <c r="F49" s="14" t="inlineStr">
+        <is>
+          <t>الأولى بعكس واحد. الثانية مرفوضة 409 حتى تُبطَل دفعاتها</t>
+        </is>
+      </c>
+      <c r="G49" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H49" s="14" t="inlineStr">
+        <is>
+          <t>حالات حدّية</t>
+        </is>
+      </c>
+      <c r="I49" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J49" s="14" t="n"/>
+      <c r="K49" s="13" t="n"/>
+      <c r="L49" s="14" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-049</t>
+        </is>
+      </c>
+      <c r="B50" s="14" t="inlineStr">
+        <is>
+          <t>الترحيل التلقائي</t>
+        </is>
+      </c>
+      <c r="C50" s="15" t="inlineStr">
+        <is>
+          <t>فاتورة محلية مباشرة: ما استُلم للمخزون والباقي مصروف</t>
+        </is>
+      </c>
+      <c r="D50" s="14" t="inlineStr">
+        <is>
+          <t>فاتورة مورد مباشرة ببند مخزون وبند خدمة</t>
+        </is>
+      </c>
+      <c r="E50" s="14" t="inlineStr">
+        <is>
+          <t>1. اعتمد الفاتورة</t>
+        </is>
+      </c>
+      <c r="F50" s="14" t="inlineStr">
+        <is>
+          <t>مدين المخزون وتكلفة المشتريات المباشرة وضريبة المدخلات، دائن المورد بإجمالي الفاتورة</t>
+        </is>
+      </c>
+      <c r="G50" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H50" s="14" t="inlineStr">
+        <is>
+          <t>تكامل</t>
+        </is>
+      </c>
+      <c r="I50" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J50" s="14" t="n"/>
+      <c r="K50" s="13" t="n"/>
+      <c r="L50" s="14" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-050</t>
+        </is>
+      </c>
+      <c r="B51" s="14" t="inlineStr">
+        <is>
+          <t>الترحيل التلقائي</t>
+        </is>
+      </c>
+      <c r="C51" s="15" t="inlineStr">
+        <is>
+          <t>مخزون أول المدة يُرحَّل مقابل الرصيد الافتتاحي لحقوق الملكية</t>
+        </is>
+      </c>
+      <c r="D51" s="14" t="inlineStr">
+        <is>
+          <t>رصيد مخزون افتتاحي مُدخل</t>
+        </is>
+      </c>
+      <c r="E51" s="14" t="inlineStr">
+        <is>
+          <t>1. أدخل رصيدًا افتتاحيًا لصنف
+2. افتح القيد</t>
+        </is>
+      </c>
+      <c r="F51" s="14" t="inlineStr">
+        <is>
+          <t>مدين المخزون ودائن 3301 بقيمة الكمية × التكلفة</t>
+        </is>
+      </c>
+      <c r="G51" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H51" s="14" t="inlineStr">
+        <is>
+          <t>تكامل</t>
+        </is>
+      </c>
+      <c r="I51" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J51" s="14" t="n"/>
+      <c r="K51" s="13" t="n"/>
+      <c r="L51" s="14" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-051</t>
+        </is>
+      </c>
+      <c r="B52" s="14" t="inlineStr">
+        <is>
+          <t>الترحيل التلقائي</t>
+        </is>
+      </c>
+      <c r="C52" s="15" t="inlineStr">
+        <is>
+          <t>الشحنة المستوردة: ضريبة الاستيراد والتكاليف المرسملة مقابل مستحق الجمارك</t>
+        </is>
+      </c>
+      <c r="D52" s="14" t="inlineStr">
+        <is>
+          <t>شحنة استيراد بتصريح جمركي وتكاليف هبوط</t>
+        </is>
+      </c>
+      <c r="E52" s="14" t="inlineStr">
+        <is>
+          <t>1. سجّل التصريح والتكاليف
+2. افتح قيدي الضريبة والتكاليف</t>
+        </is>
+      </c>
+      <c r="F52" s="14" t="inlineStr">
+        <is>
+          <t>مدين ضريبة المدخلات 1140 دائن مستحقات الجمارك 2104؛ والتكاليف تُرسمل على المخزون المتبقي والباقي مصروف</t>
+        </is>
+      </c>
+      <c r="G52" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H52" s="14" t="inlineStr">
+        <is>
+          <t>تكامل</t>
+        </is>
+      </c>
+      <c r="I52" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J52" s="14" t="n"/>
+      <c r="K52" s="13" t="n"/>
+      <c r="L52" s="14" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-052</t>
+        </is>
+      </c>
+      <c r="B53" s="14" t="inlineStr">
+        <is>
+          <t>الترحيل التلقائي</t>
+        </is>
+      </c>
+      <c r="C53" s="15" t="inlineStr">
+        <is>
+          <t>الرواتب المعتمدة: GOSI صاحب العمل وفئات الخصومات ثم الدفع</t>
+        </is>
+      </c>
+      <c r="D53" s="14" t="inlineStr">
+        <is>
+          <t>مسيّر رواتب شهر معتمد وفيه خصم سلفة وغرامة</t>
+        </is>
+      </c>
+      <c r="E53" s="14" t="inlineStr">
+        <is>
+          <t>1. اعتمد المسيّر بشخص ثانٍ
+2. افتح قيد الاستحقاق
+3. سجّل الدفع وافتح قيده</t>
+        </is>
+      </c>
+      <c r="F53" s="14" t="inlineStr">
+        <is>
+          <t>استحقاق: مصروف الرواتب وGOSI صاحب العمل، السلفة تُقفل من 1120 للموظف، الغرامة إلى 4201 إيراد آخر، دائن 2120 بصافي كل موظف. الدفع: مدين 2120 دائن 1103</t>
+        </is>
+      </c>
+      <c r="G53" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H53" s="14" t="inlineStr">
+        <is>
+          <t>تكامل</t>
+        </is>
+      </c>
+      <c r="I53" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J53" s="14" t="n"/>
+      <c r="K53" s="13" t="n"/>
+      <c r="L53" s="14" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-053</t>
+        </is>
+      </c>
+      <c r="B54" s="14" t="inlineStr">
+        <is>
+          <t>الترحيل التلقائي</t>
+        </is>
+      </c>
+      <c r="C54" s="15" t="inlineStr">
+        <is>
+          <t>العمولات: يُرحَّل التغيّر في المستحق صعودًا ثم عكسًا</t>
+        </is>
+      </c>
+      <c r="D54" s="14" t="inlineStr">
+        <is>
+          <t>عمولة مستحقة ثم استرجاع (clawback)</t>
+        </is>
+      </c>
+      <c r="E54" s="14" t="inlineStr">
+        <is>
+          <t>1. اجعل العمولة مستحقة
+2. أدخل الاسترجاع
+3. شغّل الترحيل</t>
+        </is>
+      </c>
+      <c r="F54" s="14" t="inlineStr">
+        <is>
+          <t>قيد بالزيادة (6105 مدين و2122 دائن) ثم قيد بالنقص، بحيث يساوي رصيد 2122 المستحق الفعلي</t>
+        </is>
+      </c>
+      <c r="G54" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H54" s="14" t="inlineStr">
+        <is>
+          <t>تكامل</t>
+        </is>
+      </c>
+      <c r="I54" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J54" s="14" t="n"/>
+      <c r="K54" s="13" t="n"/>
+      <c r="L54" s="14" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-054</t>
+        </is>
+      </c>
+      <c r="B55" s="14" t="inlineStr">
+        <is>
+          <t>الترحيل التلقائي</t>
+        </is>
+      </c>
+      <c r="C55" s="15" t="inlineStr">
+        <is>
+          <t>فحوص التسوية: الميزان، الذمم، الموردون، المخزون، GRNI</t>
+        </is>
+      </c>
+      <c r="D55" s="14" t="inlineStr">
+        <is>
+          <t>مستندات مرحّلة</t>
+        </is>
+      </c>
+      <c r="E55" s="14" t="inlineStr">
+        <is>
+          <t>1. افتح /accounting/reports/reconciliation أو لوحة الحسابات</t>
+        </is>
+      </c>
+      <c r="F55" s="14" t="inlineStr">
+        <is>
+          <t>كل فحص يطابق أرصدة الدفتر مع المستندات (ذمم العملاء، الموردون، المخزون، GRNI) ويوضّح الفرق إن وُجد</t>
+        </is>
+      </c>
+      <c r="G55" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H55" s="14" t="inlineStr">
+        <is>
+          <t>تكامل</t>
+        </is>
+      </c>
+      <c r="I55" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J55" s="14" t="n"/>
+      <c r="K55" s="13" t="n"/>
+      <c r="L55" s="14" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-055</t>
+        </is>
+      </c>
+      <c r="B56" s="14" t="inlineStr">
+        <is>
+          <t>ضريبة القيمة المضافة</t>
+        </is>
+      </c>
+      <c r="C56" s="15" t="inlineStr">
+        <is>
+          <t>لا تُعدّ إقرارًا ما دامت المنشأة غير مسجلة، لكن مراقب الحد يعمل</t>
+        </is>
+      </c>
+      <c r="D56" s="14" t="inlineStr">
+        <is>
+          <t>الشركة غير مسجلة في الضريبة</t>
+        </is>
+      </c>
+      <c r="E56" s="14" t="inlineStr">
+        <is>
+          <t>1. افتح /accounting/vat وحاول إعداد إقرار</t>
+        </is>
+      </c>
+      <c r="F56" s="14" t="inlineStr">
+        <is>
+          <t>رفض الإعداد برسالة «غير مسجلة»، ويظهر مراقب حد التسجيل (375,000 إلزامي / 187,500 اختياري) بإجمالي التوريدات الـ12 شهرًا</t>
+        </is>
+      </c>
+      <c r="G56" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H56" s="14" t="inlineStr">
+        <is>
+          <t>حالات حدّية</t>
+        </is>
+      </c>
+      <c r="I56" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J56" s="14" t="n"/>
+      <c r="K56" s="13" t="n"/>
+      <c r="L56" s="14" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-056</t>
+        </is>
+      </c>
+      <c r="B57" s="14" t="inlineStr">
+        <is>
+          <t>ضريبة القيمة المضافة</t>
+        </is>
+      </c>
+      <c r="C57" s="15" t="inlineStr">
+        <is>
+          <t>إقرار من أسطر مرمّزة يطابق حسابي الضريبة</t>
+        </is>
+      </c>
+      <c r="D57" s="14" t="inlineStr">
+        <is>
+          <t>الشركة مسجلة؛ فواتير ومشتريات بأكواد ضريبة</t>
+        </is>
+      </c>
+      <c r="E57" s="14" t="inlineStr">
+        <is>
+          <t>1. أعدّ إقرارًا للفترة
+2. قارن المربعات مع أرصدة 2110 و1140</t>
+        </is>
+      </c>
+      <c r="F57" s="14" t="inlineStr">
+        <is>
+          <t>المربعات 1–16 مملوءة من الأسطر المرمّزة، صافي الضريبة = مخرجات − مدخلات، والفرق مع الدفتر 0.00</t>
+        </is>
+      </c>
+      <c r="G57" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H57" s="14" t="inlineStr">
+        <is>
+          <t>وظيفي</t>
+        </is>
+      </c>
+      <c r="I57" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J57" s="14" t="n"/>
+      <c r="K57" s="13" t="n"/>
+      <c r="L57" s="14" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-057</t>
+        </is>
+      </c>
+      <c r="B58" s="14" t="inlineStr">
+        <is>
+          <t>ضريبة القيمة المضافة</t>
+        </is>
+      </c>
+      <c r="C58" s="15" t="inlineStr">
+        <is>
+          <t>قيد يدوي على حساب ضريبة بلا كود يظهر كفرق ويمنع التقديم</t>
+        </is>
+      </c>
+      <c r="D58" s="14" t="inlineStr">
+        <is>
+          <t>قيد يدوي على 2110 بلا كود</t>
+        </is>
+      </c>
+      <c r="E58" s="14" t="inlineStr">
+        <is>
+          <t>1. أعدّ إقرارًا
+2. حاول التقديم</t>
+        </is>
+      </c>
+      <c r="F58" s="14" t="inlineStr">
+        <is>
+          <t>يظهر فرق غير صفري، والتقديم مرفوض 409 حتى يُعكس القيد ويُعاد بكود صحيح</t>
+        </is>
+      </c>
+      <c r="G58" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H58" s="14" t="inlineStr">
+        <is>
+          <t>حالات حدّية</t>
+        </is>
+      </c>
+      <c r="I58" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J58" s="14" t="n"/>
+      <c r="K58" s="13" t="n"/>
+      <c r="L58" s="14" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-058</t>
+        </is>
+      </c>
+      <c r="B59" s="14" t="inlineStr">
+        <is>
+          <t>ضريبة القيمة المضافة</t>
+        </is>
+      </c>
+      <c r="C59" s="15" t="inlineStr">
+        <is>
+          <t>فترتان متداخلتان مرفوضتان، وإعادة إعداد الفترة نفسها تحدّث ولا تكرّر</t>
+        </is>
+      </c>
+      <c r="D59" s="14" t="inlineStr">
+        <is>
+          <t>إقرار مسودة لفترة</t>
+        </is>
+      </c>
+      <c r="E59" s="14" t="inlineStr">
+        <is>
+          <t>1. أعدّ إقرارًا لفترة تتداخل مع الأول
+2. أعدّ الفترة نفسها مرة ثانية</t>
+        </is>
+      </c>
+      <c r="F59" s="14" t="inlineStr">
+        <is>
+          <t>الأول مرفوض. الثاني يحدّث المسودة نفسها بلا تكرار</t>
+        </is>
+      </c>
+      <c r="G59" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H59" s="14" t="inlineStr">
+        <is>
+          <t>حالات حدّية</t>
+        </is>
+      </c>
+      <c r="I59" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J59" s="14" t="n"/>
+      <c r="K59" s="13" t="n"/>
+      <c r="L59" s="14" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-059</t>
+        </is>
+      </c>
+      <c r="B60" s="14" t="inlineStr">
+        <is>
+          <t>ضريبة القيمة المضافة</t>
+        </is>
+      </c>
+      <c r="C60" s="15" t="inlineStr">
+        <is>
+          <t>تصدير الإقرار إلى Excel</t>
+        </is>
+      </c>
+      <c r="D60" s="14" t="inlineStr">
+        <is>
+          <t>إقرار معدّ</t>
+        </is>
+      </c>
+      <c r="E60" s="14" t="inlineStr">
+        <is>
+          <t>1. اضغط تصدير Excel</t>
+        </is>
+      </c>
+      <c r="F60" s="14" t="inlineStr">
+        <is>
+          <t>ملف بمربعات الإقرار مفصّلة (المبلغ والضريبة) ومطابقة الدفتر</t>
+        </is>
+      </c>
+      <c r="G60" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H60" s="14" t="inlineStr">
+        <is>
+          <t>واجهة وعرض</t>
+        </is>
+      </c>
+      <c r="I60" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J60" s="14" t="n"/>
+      <c r="K60" s="13" t="n"/>
+      <c r="L60" s="14" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-060</t>
+        </is>
+      </c>
+      <c r="B61" s="14" t="inlineStr">
+        <is>
+          <t>ضريبة القيمة المضافة</t>
+        </is>
+      </c>
+      <c r="C61" s="15" t="inlineStr">
+        <is>
+          <t>تقديم الإقرار يُنشئ قيد التسوية</t>
+        </is>
+      </c>
+      <c r="D61" s="14" t="inlineStr">
+        <is>
+          <t>إقرار مسودة بلا فرق</t>
+        </is>
+      </c>
+      <c r="E61" s="14" t="inlineStr">
+        <is>
+          <t>1. قدّم الإقرار
+2. افتح قيد التسوية</t>
+        </is>
+      </c>
+      <c r="F61" s="14" t="inlineStr">
+        <is>
+          <t>يصبح filed، والقيد يصفّر 2110 و1140 ويرحّل الصافي إلى 2111 (ضريبة مستحقة/مستردة) وهو متوازن. التقديم الثاني والإعداد لنفس الفترة 409</t>
+        </is>
+      </c>
+      <c r="G61" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H61" s="14" t="inlineStr">
+        <is>
+          <t>وظيفي</t>
+        </is>
+      </c>
+      <c r="I61" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J61" s="14" t="n"/>
+      <c r="K61" s="13" t="n"/>
+      <c r="L61" s="14" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-061</t>
+        </is>
+      </c>
+      <c r="B62" s="14" t="inlineStr">
+        <is>
+          <t>ضريبة القيمة المضافة</t>
+        </is>
+      </c>
+      <c r="C62" s="15" t="inlineStr">
+        <is>
+          <t>إلغاء التقديم يحتاج ledger.close ويعكس التسوية مرة واحدة</t>
+        </is>
+      </c>
+      <c r="D62" s="14" t="inlineStr">
+        <is>
+          <t>إقرار مقدّم</t>
+        </is>
+      </c>
+      <c r="E62" s="14" t="inlineStr">
+        <is>
+          <t>1. بدور المحاسب اضغط «إلغاء التقديم»
+2. بدور المدير العام بسبب
+3. قدّمه مجددًا</t>
+        </is>
+      </c>
+      <c r="F62" s="14" t="inlineStr">
+        <is>
+          <t>المحاسب 403. المدير: يعود الإقرار مسودة وتُعكس التسوية مرة واحدة. التقديم مجددًا ينجح ويصفّر الحسابين</t>
+        </is>
+      </c>
+      <c r="G62" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H62" s="14" t="inlineStr">
+        <is>
+          <t>صلاحيات</t>
+        </is>
+      </c>
+      <c r="I62" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J62" s="14" t="n"/>
+      <c r="K62" s="13" t="n"/>
+      <c r="L62" s="14" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-062</t>
+        </is>
+      </c>
+      <c r="B63" s="14" t="inlineStr">
+        <is>
+          <t>ضريبة القيمة المضافة</t>
+        </is>
+      </c>
+      <c r="C63" s="15" t="inlineStr">
+        <is>
+          <t>مستند معكوس يصافي نفسه في الإقرار</t>
+        </is>
+      </c>
+      <c r="D63" s="14" t="inlineStr">
+        <is>
+          <t>فاتورة مرحّلة ثم ملغاة</t>
+        </is>
+      </c>
+      <c r="E63" s="14" t="inlineStr">
+        <is>
+          <t>1. أعدّ الإقرار للفترة</t>
+        </is>
+      </c>
+      <c r="F63" s="14" t="inlineStr">
+        <is>
+          <t>أساس الضريبة للفاتورة والعكس يصافيان إلى صفر فلا يظهر البيع في المربعات</t>
+        </is>
+      </c>
+      <c r="G63" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H63" s="14" t="inlineStr">
+        <is>
+          <t>حالات حدّية</t>
+        </is>
+      </c>
+      <c r="I63" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J63" s="14" t="n"/>
+      <c r="K63" s="13" t="n"/>
+      <c r="L63" s="14" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-063</t>
+        </is>
+      </c>
+      <c r="B64" s="14" t="inlineStr">
+        <is>
+          <t>التسوية البنكية</t>
+        </is>
+      </c>
+      <c r="C64" s="15" t="inlineStr">
+        <is>
+          <t>كشف على حساب غير بنكي أو غير متّزن الأرصدة يُرفض</t>
+        </is>
+      </c>
+      <c r="D64" s="14" t="inlineStr">
+        <is>
+          <t>حساب نقدية وبنك</t>
+        </is>
+      </c>
+      <c r="E64" s="14" t="inlineStr">
+        <is>
+          <t>1. ارفع كشفًا على حساب مصروف
+2. ارفع كشفًا ورصيده الختامي ≠ الافتتاحي + الحركات</t>
+        </is>
+      </c>
+      <c r="F64" s="14" t="inlineStr">
+        <is>
+          <t>رفض 400 في الحالتين برسالة واضحة</t>
+        </is>
+      </c>
+      <c r="G64" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H64" s="14" t="inlineStr">
+        <is>
+          <t>تحقق من المدخلات</t>
+        </is>
+      </c>
+      <c r="I64" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J64" s="14" t="n"/>
+      <c r="K64" s="13" t="n"/>
+      <c r="L64" s="14" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-064</t>
+        </is>
+      </c>
+      <c r="B65" s="14" t="inlineStr">
+        <is>
+          <t>التسوية البنكية</t>
+        </is>
+      </c>
+      <c r="C65" s="15" t="inlineStr">
+        <is>
+          <t>مطابقة بالمبلغ والتاريخ تُظهر الفرق وتُسوّى عند صفر</t>
+        </is>
+      </c>
+      <c r="D65" s="14" t="inlineStr">
+        <is>
+          <t>كشف بنكي بحركات توافق قيودًا في الدفتر</t>
+        </is>
+      </c>
+      <c r="E65" s="14" t="inlineStr">
+        <is>
+          <t>1. افتح الكشف واضغط «مطابقة تلقائية»
+2. طابق ما تبقى يدويًا
+3. اضغط «اعتماد التسوية»</t>
+        </is>
+      </c>
+      <c r="F65" s="14" t="inlineStr">
+        <is>
+          <t>تظهر الفروق بين رصيد الدفتر والكشف، وتُعتمد التسوية فقط عندما يصبح الفرق صفرًا</t>
+        </is>
+      </c>
+      <c r="G65" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H65" s="14" t="inlineStr">
+        <is>
+          <t>وظيفي</t>
+        </is>
+      </c>
+      <c r="I65" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J65" s="14" t="n"/>
+      <c r="K65" s="13" t="n"/>
+      <c r="L65" s="14" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-065</t>
+        </is>
+      </c>
+      <c r="B66" s="14" t="inlineStr">
+        <is>
+          <t>التسوية البنكية</t>
+        </is>
+      </c>
+      <c r="C66" s="15" t="inlineStr">
+        <is>
+          <t>سطر دفتر مطابَق لا يُطابَق ثانية في كشف آخر</t>
+        </is>
+      </c>
+      <c r="D66" s="14" t="inlineStr">
+        <is>
+          <t>سطر دفتر مطابق في كشف</t>
+        </is>
+      </c>
+      <c r="E66" s="14" t="inlineStr">
+        <is>
+          <t>1. افتح كشفًا آخر وحاول مطابقة السطر نفسه</t>
+        </is>
+      </c>
+      <c r="F66" s="14" t="inlineStr">
+        <is>
+          <t>رفض 409 (السطر مطابق) ولا تتغير التسوية الأولى</t>
+        </is>
+      </c>
+      <c r="G66" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H66" s="14" t="inlineStr">
+        <is>
+          <t>حالات حدّية</t>
+        </is>
+      </c>
+      <c r="I66" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J66" s="14" t="n"/>
+      <c r="K66" s="13" t="n"/>
+      <c r="L66" s="14" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-066</t>
+        </is>
+      </c>
+      <c r="B67" s="14" t="inlineStr">
+        <is>
+          <t>الأصول الثابتة والمخصصات</t>
+        </is>
+      </c>
+      <c r="C67" s="15" t="inlineStr">
+        <is>
+          <t>تسجيل أصل مشترى بقيد وربطه بحساب الأصل والإهلاك</t>
+        </is>
+      </c>
+      <c r="D67" s="14" t="inlineStr">
+        <is>
+          <t>قيد شراء أصل مرحّل</t>
+        </is>
+      </c>
+      <c r="E67" s="14" t="inlineStr">
+        <is>
+          <t>1. افتح /accounting/assets وسجّل الأصل
+2. اختر حساب الأصل والإهلاك المتراكم ومصروف الإهلاك والعمر</t>
+        </is>
+      </c>
+      <c r="F67" s="14" t="inlineStr">
+        <is>
+          <t>يُسجَّل الأصل بالحسابات الصحيحة ويظهر في السجل بتكلفته وتاريخ بدء الإهلاك</t>
+        </is>
+      </c>
+      <c r="G67" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H67" s="14" t="inlineStr">
+        <is>
+          <t>وظيفي</t>
+        </is>
+      </c>
+      <c r="I67" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J67" s="14" t="n"/>
+      <c r="K67" s="13" t="n"/>
+      <c r="L67" s="14" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-067</t>
+        </is>
+      </c>
+      <c r="B68" s="14" t="inlineStr">
+        <is>
+          <t>الأصول الثابتة والمخصصات</t>
+        </is>
+      </c>
+      <c r="C68" s="15" t="inlineStr">
+        <is>
+          <t>الإهلاك الشهري بقيد واحد، يُعوّض الأشهر السابقة، ولا يتكرر</t>
+        </is>
+      </c>
+      <c r="D68" s="14" t="inlineStr">
+        <is>
+          <t>أصل مسجّل من عدة أشهر</t>
+        </is>
+      </c>
+      <c r="E68" s="14" t="inlineStr">
+        <is>
+          <t>1. شغّل الإهلاك لشهر منتهٍ
+2. شغّل الشهر نفسه ثانية</t>
+        </is>
+      </c>
+      <c r="F68" s="14" t="inlineStr">
+        <is>
+          <t>قيد واحد لكل تشغيل يشمل الأشهر الفائتة غير المهلكة. التشغيل الثاني لا يُنشئ شيئًا</t>
+        </is>
+      </c>
+      <c r="G68" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H68" s="14" t="inlineStr">
+        <is>
+          <t>وظيفي</t>
+        </is>
+      </c>
+      <c r="I68" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J68" s="14" t="n"/>
+      <c r="K68" s="13" t="n"/>
+      <c r="L68" s="14" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-068</t>
+        </is>
+      </c>
+      <c r="B69" s="14" t="inlineStr">
+        <is>
+          <t>الأصول الثابتة والمخصصات</t>
+        </is>
+      </c>
+      <c r="C69" s="15" t="inlineStr">
+        <is>
+          <t>تشغيل شهر لم ينتهِ أو قبل البدء، وتعديل أصل بدأ إهلاكه، مرفوضان</t>
+        </is>
+      </c>
+      <c r="D69" s="14" t="inlineStr">
+        <is>
+          <t>أصل مهلك</t>
+        </is>
+      </c>
+      <c r="E69" s="14" t="inlineStr">
+        <is>
+          <t>1. شغّل الإهلاك للشهر الحالي
+2. شغّل لشهر قبل تاريخ البدء
+3. عدّل تكلفة أصل بدأ إهلاكه</t>
+        </is>
+      </c>
+      <c r="F69" s="14" t="inlineStr">
+        <is>
+          <t>الكل مرفوض برسالة سبب</t>
+        </is>
+      </c>
+      <c r="G69" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H69" s="14" t="inlineStr">
+        <is>
+          <t>حالات حدّية</t>
+        </is>
+      </c>
+      <c r="I69" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J69" s="14" t="n"/>
+      <c r="K69" s="13" t="n"/>
+      <c r="L69" s="14" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-069</t>
+        </is>
+      </c>
+      <c r="B70" s="14" t="inlineStr">
+        <is>
+          <t>الأصول الثابتة والمخصصات</t>
+        </is>
+      </c>
+      <c r="C70" s="15" t="inlineStr">
+        <is>
+          <t>استبعاد أصل يُهلكه حتى شهر الاستبعاد ويرحّل الربح أو الخسارة</t>
+        </is>
+      </c>
+      <c r="D70" s="14" t="inlineStr">
+        <is>
+          <t>أصل بقيمة دفترية</t>
+        </is>
+      </c>
+      <c r="E70" s="14" t="inlineStr">
+        <is>
+          <t>1. استبعد الأصل بسعر بيع
+2. افتح القيد</t>
+        </is>
+      </c>
+      <c r="F70" s="14" t="inlineStr">
+        <is>
+          <t>إهلاك حتى شهر الاستبعاد ثم قيد يُقفل التكلفة والمتراكم ويثبّت ربحًا/خسارة بقدر الفرق</t>
+        </is>
+      </c>
+      <c r="G70" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H70" s="14" t="inlineStr">
+        <is>
+          <t>وظيفي</t>
+        </is>
+      </c>
+      <c r="I70" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J70" s="14" t="n"/>
+      <c r="K70" s="13" t="n"/>
+      <c r="L70" s="14" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-070</t>
+        </is>
+      </c>
+      <c r="B71" s="14" t="inlineStr">
+        <is>
+          <t>الأصول الثابتة والمخصصات</t>
+        </is>
+      </c>
+      <c r="C71" s="15" t="inlineStr">
+        <is>
+          <t>مخصص نهاية الخدمة حسب المادة 84 يُحسب لكل موظف ويُرحَّل مرة واحدة</t>
+        </is>
+      </c>
+      <c r="D71" s="14" t="inlineStr">
+        <is>
+          <t>موظفون بتواريخ تعيين ورواتب</t>
+        </is>
+      </c>
+      <c r="E71" s="14" t="inlineStr">
+        <is>
+          <t>1. افتح مخصص نهاية الخدمة واحسب
+2. رحّل المخصص
+3. أعد الترحيل</t>
+        </is>
+      </c>
+      <c r="F71" s="14" t="inlineStr">
+        <is>
+          <t>الاستحقاق نصف شهر عن أول 5 سنوات وشهر كامل بعدها (المادة 84) لكل موظف. الترحيل الثاني لا يُنشئ شيئًا</t>
+        </is>
+      </c>
+      <c r="G71" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H71" s="14" t="inlineStr">
+        <is>
+          <t>وظيفي</t>
+        </is>
+      </c>
+      <c r="I71" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J71" s="14" t="n"/>
+      <c r="K71" s="13" t="n"/>
+      <c r="L71" s="14" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-071</t>
+        </is>
+      </c>
+      <c r="B72" s="14" t="inlineStr">
+        <is>
+          <t>القوائم الإضافية</t>
+        </is>
+      </c>
+      <c r="C72" s="15" t="inlineStr">
+        <is>
+          <t>التدفقات النقدية تطابق التغيّر في النقد</t>
+        </is>
+      </c>
+      <c r="D72" s="14" t="inlineStr">
+        <is>
+          <t>حركات نقد وبنك في الفترة</t>
+        </is>
+      </c>
+      <c r="E72" s="14" t="inlineStr">
+        <is>
+          <t>1. افتح قائمة التدفقات النقدية للفترة</t>
+        </is>
+      </c>
+      <c r="F72" s="14" t="inlineStr">
+        <is>
+          <t>صافي التدفقات = رصيد النقد آخر الفترة − أولها</t>
+        </is>
+      </c>
+      <c r="G72" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H72" s="14" t="inlineStr">
+        <is>
+          <t>وظيفي</t>
+        </is>
+      </c>
+      <c r="I72" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J72" s="14" t="n"/>
+      <c r="K72" s="13" t="n"/>
+      <c r="L72" s="14" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-072</t>
+        </is>
+      </c>
+      <c r="B73" s="14" t="inlineStr">
+        <is>
+          <t>القوائم الإضافية</t>
+        </is>
+      </c>
+      <c r="C73" s="15" t="inlineStr">
+        <is>
+          <t>التغيّرات في حقوق الملكية تقفل على حقوق الملكية في الميزانية</t>
+        </is>
+      </c>
+      <c r="D73" s="14" t="inlineStr">
+        <is>
+          <t>رأس مال وأرباح مرحّلة وربح السنة</t>
+        </is>
+      </c>
+      <c r="E73" s="14" t="inlineStr">
+        <is>
+          <t>1. افتح قائمة التغيّرات في حقوق الملكية</t>
+        </is>
+      </c>
+      <c r="F73" s="14" t="inlineStr">
+        <is>
+          <t>الرصيد الختامي = حقوق الملكية في الميزانية + ربح الفترة</t>
+        </is>
+      </c>
+      <c r="G73" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H73" s="14" t="inlineStr">
+        <is>
+          <t>وظيفي</t>
+        </is>
+      </c>
+      <c r="I73" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J73" s="14" t="n"/>
+      <c r="K73" s="13" t="n"/>
+      <c r="L73" s="14" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-073</t>
+        </is>
+      </c>
+      <c r="B74" s="14" t="inlineStr">
+        <is>
+          <t>القوائم الإضافية</t>
+        </is>
+      </c>
+      <c r="C74" s="15" t="inlineStr">
+        <is>
+          <t>أعمار الديون تطابق حسابي العملاء والموردين</t>
+        </is>
+      </c>
+      <c r="D74" s="14" t="inlineStr">
+        <is>
+          <t>فواتير مفتوحة بأعمار مختلفة</t>
+        </is>
+      </c>
+      <c r="E74" s="14" t="inlineStr">
+        <is>
+          <t>1. افتح أعمار الذمم المدينة ثم الدائنة</t>
+        </is>
+      </c>
+      <c r="F74" s="14" t="inlineStr">
+        <is>
+          <t>مجاميع الأعمار (FIFO) = رصيد 1110 و2101 على الترتيب</t>
+        </is>
+      </c>
+      <c r="G74" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H74" s="14" t="inlineStr">
+        <is>
+          <t>وظيفي</t>
+        </is>
+      </c>
+      <c r="I74" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J74" s="14" t="n"/>
+      <c r="K74" s="13" t="n"/>
+      <c r="L74" s="14" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-074</t>
+        </is>
+      </c>
+      <c r="B75" s="14" t="inlineStr">
+        <is>
+          <t>القوائم الإضافية</t>
+        </is>
+      </c>
+      <c r="C75" s="15" t="inlineStr">
+        <is>
+          <t>جدول وعاء الزكاة: الإضافات − الحسومات وقاعدة الأكبر</t>
+        </is>
+      </c>
+      <c r="D75" s="14" t="inlineStr">
+        <is>
+          <t>ميزانية ببنود زكوية</t>
+        </is>
+      </c>
+      <c r="E75" s="14" t="inlineStr">
+        <is>
+          <t>1. افتح جدول الزكاة للسنة</t>
+        </is>
+      </c>
+      <c r="F75" s="14" t="inlineStr">
+        <is>
+          <t>الوعاء = حقوق الملكية + الإضافات − الحسومات، والوعاء الخاضع هو الأكبر من الوعاء والربح المعدّل</t>
+        </is>
+      </c>
+      <c r="G75" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H75" s="14" t="inlineStr">
+        <is>
+          <t>وظيفي</t>
+        </is>
+      </c>
+      <c r="I75" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J75" s="14" t="n"/>
+      <c r="K75" s="13" t="n"/>
+      <c r="L75" s="14" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-075</t>
+        </is>
+      </c>
+      <c r="B76" s="14" t="inlineStr">
+        <is>
+          <t>الإقفال وحزمة المراجع</t>
+        </is>
+      </c>
+      <c r="C76" s="15" t="inlineStr">
+        <is>
+          <t>السنة التي لم تنتهِ لا تُقفل ويظهر سبب المنع</t>
+        </is>
+      </c>
+      <c r="D76" s="14" t="inlineStr">
+        <is>
+          <t>السنة الحالية مفتوحة</t>
+        </is>
+      </c>
+      <c r="E76" s="14" t="inlineStr">
+        <is>
+          <t>1. افتح /accounting/closing
+2. حاول إقفال السنة الحالية</t>
+        </is>
+      </c>
+      <c r="F76" s="14" t="inlineStr">
+        <is>
+          <t>تظهر السنة بحالة مفتوحة ولا يُفعَّل الزر مع سبب «لم تنتهِ»؛ المحاسب 403 والمدير 409</t>
+        </is>
+      </c>
+      <c r="G76" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H76" s="14" t="inlineStr">
+        <is>
+          <t>حالات حدّية</t>
+        </is>
+      </c>
+      <c r="I76" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J76" s="14" t="n"/>
+      <c r="K76" s="13" t="n"/>
+      <c r="L76" s="14" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-076</t>
+        </is>
+      </c>
+      <c r="B77" s="14" t="inlineStr">
+        <is>
+          <t>الإقفال وحزمة المراجع</t>
+        </is>
+      </c>
+      <c r="C77" s="15" t="inlineStr">
+        <is>
+          <t>إقفال سنة منتهية يرحّل الإيراد والمصروف إلى الأرباح المبقاة ويقفل الدفاتر</t>
+        </is>
+      </c>
+      <c r="D77" s="14" t="inlineStr">
+        <is>
+          <t>سنة منتهية فيها إيراد 5,000 ومصروف 2,000</t>
+        </is>
+      </c>
+      <c r="E77" s="14" t="inlineStr">
+        <is>
+          <t>1. اضغط «إقفال السنة» بدور المدير
+2. افتح قائمة الدخل والميزانية
+3. حاول إضافة قيد بتاريخ داخل السنة</t>
+        </is>
+      </c>
+      <c r="F77" s="14" t="inlineStr">
+        <is>
+          <t>قيد closing بربح 3,000 يصفّر الإيراد والمصروف ويرحّله إلى 3201. قائمة الدخل تبقى تُظهر الربح والميزانية متوازنة. القيد الجديد في السنة المقفلة مرفوض</t>
+        </is>
+      </c>
+      <c r="G77" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H77" s="14" t="inlineStr">
+        <is>
+          <t>وظيفي</t>
+        </is>
+      </c>
+      <c r="I77" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J77" s="14" t="n"/>
+      <c r="K77" s="13" t="n"/>
+      <c r="L77" s="14" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-077</t>
+        </is>
+      </c>
+      <c r="B78" s="14" t="inlineStr">
+        <is>
+          <t>الإقفال وحزمة المراجع</t>
+        </is>
+      </c>
+      <c r="C78" s="15" t="inlineStr">
+        <is>
+          <t>لا تُقفل السنة الحالية قبل السابقة</t>
+        </is>
+      </c>
+      <c r="D78" s="14" t="inlineStr">
+        <is>
+          <t>سنة سابقة مفتوحة</t>
+        </is>
+      </c>
+      <c r="E78" s="14" t="inlineStr">
+        <is>
+          <t>1. افتح السنوات المالية</t>
+        </is>
+      </c>
+      <c r="F78" s="14" t="inlineStr">
+        <is>
+          <t>سنة لاحقة تظهر بسبب «أقفل السنة السابقة أولًا» ولا يمكن إقفالها</t>
+        </is>
+      </c>
+      <c r="G78" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H78" s="14" t="inlineStr">
+        <is>
+          <t>حالات حدّية</t>
+        </is>
+      </c>
+      <c r="I78" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J78" s="14" t="n"/>
+      <c r="K78" s="13" t="n"/>
+      <c r="L78" s="14" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-078</t>
+        </is>
+      </c>
+      <c r="B79" s="14" t="inlineStr">
+        <is>
+          <t>الإقفال وحزمة المراجع</t>
+        </is>
+      </c>
+      <c r="C79" s="15" t="inlineStr">
+        <is>
+          <t>فتح السنة المقفلة للمالك فقط ويعكس قيد الإقفال مرة واحدة</t>
+        </is>
+      </c>
+      <c r="D79" s="14" t="inlineStr">
+        <is>
+          <t>سنة مقفلة</t>
+        </is>
+      </c>
+      <c r="E79" s="14" t="inlineStr">
+        <is>
+          <t>1. بدور المدير اضغط «إعادة فتح»
+2. بدور المالك بسبب</t>
+        </is>
+      </c>
+      <c r="F79" s="14" t="inlineStr">
+        <is>
+          <t>المدير 403. المالك: يُعكس قيد الإقفال مرة واحدة وتعود الأرصدة ويصبح حالة السنة open</t>
+        </is>
+      </c>
+      <c r="G79" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H79" s="14" t="inlineStr">
+        <is>
+          <t>صلاحيات</t>
+        </is>
+      </c>
+      <c r="I79" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J79" s="14" t="n"/>
+      <c r="K79" s="13" t="n"/>
+      <c r="L79" s="14" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-079</t>
+        </is>
+      </c>
+      <c r="B80" s="14" t="inlineStr">
+        <is>
+          <t>الإقفال وحزمة المراجع</t>
+        </is>
+      </c>
+      <c r="C80" s="15" t="inlineStr">
+        <is>
+          <t>حزمة المراجع (zip) للمالك والمدير العام فقط</t>
+        </is>
+      </c>
+      <c r="D80" s="14" t="inlineStr">
+        <is>
+          <t>سنة بها بيانات</t>
+        </is>
+      </c>
+      <c r="E80" s="14" t="inlineStr">
+        <is>
+          <t>1. بدور المحاسب حمّل الحزمة
+2. بدور المدير حمّلها
+3. افتح الملف المضغوط</t>
+        </is>
+      </c>
+      <c r="F80" s="14" t="inlineStr">
+        <is>
+          <t>المحاسب 403. الحزمة تضم كل القوائم وملف manifest وسجل التدقيق وسجل الفواتير الإلكترونية، وكلها بأرقام تطابق التقارير</t>
+        </is>
+      </c>
+      <c r="G80" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H80" s="14" t="inlineStr">
+        <is>
+          <t>صلاحيات</t>
+        </is>
+      </c>
+      <c r="I80" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J80" s="14" t="n"/>
+      <c r="K80" s="13" t="n"/>
+      <c r="L80" s="14" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-080</t>
+        </is>
+      </c>
+      <c r="B81" s="14" t="inlineStr">
+        <is>
+          <t>الفوترة الإلكترونية (ZATCA)</t>
+        </is>
+      </c>
+      <c r="C81" s="15" t="inlineStr">
+        <is>
+          <t>الشاشة والتفعيل خلف الصلاحيات ولا يُفعَّل قبل الاكتمال</t>
+        </is>
+      </c>
+      <c r="D81" s="14" t="inlineStr">
+        <is>
+          <t>شركة غير مجهّزة؛ مستخدم بلا einvoice.manage</t>
+        </is>
+      </c>
+      <c r="E81" s="14" t="inlineStr">
+        <is>
+          <t>1. افتح /accounting/einvoice
+2. حاول التفعيل بدون وحدة EGS</t>
+        </is>
+      </c>
+      <c r="F81" s="14" t="inlineStr">
+        <is>
+          <t>القراءة لمن لديه ledger.read، والإدارة (إنشاء وحدات/تفعيل) لـ einvoice.manage فقط. التفعيل مرفوض مع قائمة نواقص: التسجيل الضريبي، هوية البائع، وحدة بشهادة إنتاج، عدم ربط ERPNext</t>
+        </is>
+      </c>
+      <c r="G81" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H81" s="14" t="inlineStr">
+        <is>
+          <t>صلاحيات</t>
+        </is>
+      </c>
+      <c r="I81" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J81" s="14" t="n"/>
+      <c r="K81" s="13" t="n"/>
+      <c r="L81" s="14" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-081</t>
+        </is>
+      </c>
+      <c r="B82" s="14" t="inlineStr">
+        <is>
+          <t>الفوترة الإلكترونية (ZATCA)</t>
+        </is>
+      </c>
+      <c r="C82" s="15" t="inlineStr">
+        <is>
+          <t>سُلَّم الإعداد: وحدة ← CSR وOTP ← فحوص الامتثال ← شهادة الإنتاج</t>
+        </is>
+      </c>
+      <c r="D82" s="14" t="inlineStr">
+        <is>
+          <t>هوية الشركة مكتملة (اسم، رقم ضريبي، سجل، عنوان وطني)</t>
+        </is>
+      </c>
+      <c r="E82" s="14" t="inlineStr">
+        <is>
+          <t>1. أنشئ وحدة EGS واختر البيئة
+2. ولّد الـ CSR وأدخل رمز OTP من بوابة فاتورة
+3. شغّل فحوص الامتثال (6 مستندات)
+4. اطلب شهادة الإنتاج</t>
+        </is>
+      </c>
+      <c r="F82" s="14" t="inlineStr">
+        <is>
+          <t>تتقدم الحالة: csr_generated ← compliance_csid ← compliance_passed ← production. المفتاح الخاص لا يظهر في أي شاشة أو استجابة</t>
+        </is>
+      </c>
+      <c r="G82" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H82" s="14" t="inlineStr">
+        <is>
+          <t>وظيفي</t>
+        </is>
+      </c>
+      <c r="I82" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J82" s="14" t="n"/>
+      <c r="K82" s="13" t="n"/>
+      <c r="L82" s="14" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-082</t>
+        </is>
+      </c>
+      <c r="B83" s="14" t="inlineStr">
+        <is>
+          <t>الفوترة الإلكترونية (ZATCA)</t>
+        </is>
+      </c>
+      <c r="C83" s="15" t="inlineStr">
+        <is>
+          <t>وحدة حيّة واحدة فقط</t>
+        </is>
+      </c>
+      <c r="D83" s="14" t="inlineStr">
+        <is>
+          <t>وحدة أولى حيّة بشهادة إنتاج</t>
+        </is>
+      </c>
+      <c r="E83" s="14" t="inlineStr">
+        <is>
+          <t>1. أنشئ وحدة ثانية بيئة محاكاة وأدخل OTP وشغّل فحوص الامتثال
+2. اطلب شهادة الإنتاج للوحدة الثانية
+3. ألغِ الوحدة الثانية بسبب</t>
+        </is>
+      </c>
+      <c r="F83" s="14" t="inlineStr">
+        <is>
+          <t>طلب الإنتاج مرفوض 409 لأن وحدة أخرى حيّة؛ والإلغاء ينجح ويبقى التوقيع على الأولى</t>
+        </is>
+      </c>
+      <c r="G83" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H83" s="14" t="inlineStr">
+        <is>
+          <t>حالات حدّية</t>
+        </is>
+      </c>
+      <c r="I83" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J83" s="14" t="n"/>
+      <c r="K83" s="13" t="n"/>
+      <c r="L83" s="14" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-083</t>
+        </is>
+      </c>
+      <c r="B84" s="14" t="inlineStr">
+        <is>
+          <t>الفوترة الإلكترونية (ZATCA)</t>
+        </is>
+      </c>
+      <c r="C84" s="15" t="inlineStr">
+        <is>
+          <t>تجربة الصندوق الرملي من الشاشة</t>
+        </is>
+      </c>
+      <c r="D84" s="14" t="inlineStr">
+        <is>
+          <t>اتصال بالإنترنت؛ بيئة المطوّرين</t>
+        </is>
+      </c>
+      <c r="E84" s="14" t="inlineStr">
+        <is>
+          <t>1. افتح تبويب «وحدات الإصدار والتهيئة» واضغط «تشغيل التجربة»</t>
+        </is>
+      </c>
+      <c r="F84" s="14" t="inlineStr">
+        <is>
+          <t>تمر العملية حتى شهادة الإنتاج على بوابة المطوّرين باستخدام هوية ZATCA التجريبية ورمز 123345 فقط، ولا تُرسَل بيانات الشركة</t>
+        </is>
+      </c>
+      <c r="G84" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H84" s="14" t="inlineStr">
+        <is>
+          <t>تكامل</t>
+        </is>
+      </c>
+      <c r="I84" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J84" s="14" t="n"/>
+      <c r="K84" s="13" t="n"/>
+      <c r="L84" s="14" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-084</t>
+        </is>
+      </c>
+      <c r="B85" s="14" t="inlineStr">
+        <is>
+          <t>الفوترة الإلكترونية (ZATCA)</t>
+        </is>
+      </c>
+      <c r="C85" s="15" t="inlineStr">
+        <is>
+          <t>كل فاتورة تُوقَّع بسلسلة ICV / PIH بلا فجوات</t>
+        </is>
+      </c>
+      <c r="D85" s="14" t="inlineStr">
+        <is>
+          <t>تفعيل ووحدة حيّة؛ ثلاث فواتير</t>
+        </is>
+      </c>
+      <c r="E85" s="14" t="inlineStr">
+        <is>
+          <t>1. أصدر ثلاث فواتير متتالية
+2. افتح سجل المستندات
+3. اضغط «فحص السلسلة» (ledger.close)</t>
+        </is>
+      </c>
+      <c r="F85" s="14" t="inlineStr">
+        <is>
+          <t>ICV يتزايد 1,2,3 بلا فجوة وPIH كل مستند = هاش السابق (الأول بالقيمة الأولية)، والتحقق ينجح. كل مستند UUID فريد وQR موقّع</t>
+        </is>
+      </c>
+      <c r="G85" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H85" s="14" t="inlineStr">
+        <is>
+          <t>وظيفي</t>
+        </is>
+      </c>
+      <c r="I85" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J85" s="14" t="n"/>
+      <c r="K85" s="13" t="n"/>
+      <c r="L85" s="14" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-085</t>
+        </is>
+      </c>
+      <c r="B86" s="14" t="inlineStr">
+        <is>
+          <t>الفوترة الإلكترونية (ZATCA)</t>
+        </is>
+      </c>
+      <c r="C86" s="15" t="inlineStr">
+        <is>
+          <t>الفاتورة النهائية تحمل الدفعات المقدمة كما تشترط ZATCA</t>
+        </is>
+      </c>
+      <c r="D86" s="14" t="inlineStr">
+        <is>
+          <t>عقد بدفعتين مقدمتين</t>
+        </is>
+      </c>
+      <c r="E86" s="14" t="inlineStr">
+        <is>
+          <t>1. أصدر الفاتورة النهائية 388
+2. نزّل XML من السجل</t>
+        </is>
+      </c>
+      <c r="F86" s="14" t="inlineStr">
+        <is>
+          <t>سطر بكمية صفر لكل دفعة مقدمة مع المرجع (الرقم، UUID، التاريخ، الوقت، النوع 386) وضريبته وPrepaidAmount، والإجمالي المستحق صحيح</t>
+        </is>
+      </c>
+      <c r="G86" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H86" s="14" t="inlineStr">
+        <is>
+          <t>تكامل</t>
+        </is>
+      </c>
+      <c r="I86" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J86" s="14" t="n"/>
+      <c r="K86" s="13" t="n"/>
+      <c r="L86" s="14" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-086</t>
+        </is>
+      </c>
+      <c r="B87" s="14" t="inlineStr">
+        <is>
+          <t>الفوترة الإلكترونية (ZATCA)</t>
+        </is>
+      </c>
+      <c r="C87" s="15" t="inlineStr">
+        <is>
+          <t>الفاتورة القياسية لا تُشارَك قبل الاعتماد (clearance)</t>
+        </is>
+      </c>
+      <c r="D87" s="14" t="inlineStr">
+        <is>
+          <t>فاتورة B2B مصدرة ولم تُعتمد بعد</t>
+        </is>
+      </c>
+      <c r="E87" s="14" t="inlineStr">
+        <is>
+          <t>1. حاول تنزيل PDF الفاتورة
+2. افتح الفاتورة في بوابة العميل</t>
+        </is>
+      </c>
+      <c r="F87" s="14" t="inlineStr">
+        <is>
+          <t>PDF مرفوض 409 «بانتظار اعتماد ZATCA»، والبوابة لا تعرض رمز QR ولا PDF وتُظهر حالة awaitingClearance</t>
+        </is>
+      </c>
+      <c r="G87" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H87" s="14" t="inlineStr">
+        <is>
+          <t>أمان</t>
+        </is>
+      </c>
+      <c r="I87" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J87" s="14" t="n"/>
+      <c r="K87" s="13" t="n"/>
+      <c r="L87" s="14" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-087</t>
+        </is>
+      </c>
+      <c r="B88" s="14" t="inlineStr">
+        <is>
+          <t>الفوترة الإلكترونية (ZATCA)</t>
+        </is>
+      </c>
+      <c r="C88" s="15" t="inlineStr">
+        <is>
+          <t>الاعتماد بترتيب ICV ويستبدل الـ QR المطبوع بالمختوم</t>
+        </is>
+      </c>
+      <c r="D88" s="14" t="inlineStr">
+        <is>
+          <t>ثلاث فواتير قياسية مصدرة</t>
+        </is>
+      </c>
+      <c r="E88" s="14" t="inlineStr">
+        <is>
+          <t>1. اضغط «إرسال المعلّق الآن» أو انتظر دورة الدقيقتين
+2. قارن QR قبل وبعد</t>
+        </is>
+      </c>
+      <c r="F88" s="14" t="inlineStr">
+        <is>
+          <t>تُرسَل بترتيب ICV وتصبح cleared، ويُخزَّن XML المعتمد من ZATCA، ويصير QR الفاتورة هو المختوم من ZATCA ويحلّ PDF</t>
+        </is>
+      </c>
+      <c r="G88" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H88" s="14" t="inlineStr">
+        <is>
+          <t>تكامل</t>
+        </is>
+      </c>
+      <c r="I88" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J88" s="14" t="n"/>
+      <c r="K88" s="13" t="n"/>
+      <c r="L88" s="14" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-088</t>
+        </is>
+      </c>
+      <c r="B89" s="14" t="inlineStr">
+        <is>
+          <t>الفوترة الإلكترونية (ZATCA)</t>
+        </is>
+      </c>
+      <c r="C89" s="15" t="inlineStr">
+        <is>
+          <t>الإشعار الدائن يشير للفاتورة ويحمل السبب؛ البسيطة تُبلَّغ والقياسية تُعتمد</t>
+        </is>
+      </c>
+      <c r="D89" s="14" t="inlineStr">
+        <is>
+          <t>فاتورة قياسية معتمدة وأخرى مبسطة</t>
+        </is>
+      </c>
+      <c r="E89" s="14" t="inlineStr">
+        <is>
+          <t>1. أصدر إشعار دائن على كل منهما بسبب
+2. افتح XML الإشعار</t>
+        </is>
+      </c>
+      <c r="F89" s="14" t="inlineStr">
+        <is>
+          <t>BillingReference للفاتورة الأصلية وInstructionNote بالسبب والمبالغ موجبة والجذر Invoice (لا CreditNote). القياسي يُعتمد والمبسط يُبلَّغ خلال 24 ساعة</t>
+        </is>
+      </c>
+      <c r="G89" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H89" s="14" t="inlineStr">
+        <is>
+          <t>تكامل</t>
+        </is>
+      </c>
+      <c r="I89" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J89" s="14" t="n"/>
+      <c r="K89" s="13" t="n"/>
+      <c r="L89" s="14" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-089</t>
+        </is>
+      </c>
+      <c r="B90" s="14" t="inlineStr">
+        <is>
+          <t>الفوترة الإلكترونية (ZATCA)</t>
+        </is>
+      </c>
+      <c r="C90" s="15" t="inlineStr">
+        <is>
+          <t>انقطاع ZATCA أو رفض مستند لا يكسر السلسلة</t>
+        </is>
+      </c>
+      <c r="D90" s="14" t="inlineStr">
+        <is>
+          <t>بوابة ZATCA غير متاحة ثم ترفض مستندًا</t>
+        </is>
+      </c>
+      <c r="E90" s="14" t="inlineStr">
+        <is>
+          <t>1. أصدر فاتورتين أثناء الانقطاع
+2. أعد الاتصال وأرسل
+3. ارفض مستندًا واحدًا واضغط «إعادة إصدار»</t>
+        </is>
+      </c>
+      <c r="F90" s="14" t="inlineStr">
+        <is>
+          <t>المستندات تبقى pending وتُرسَل لاحقًا بالترتيب (أخطاء 5xx مؤقتة). المرفوض يُعاد إصداره بـ ICV وUUID جديدين ويُعلَّم القديم superseded ولا تنكسر السلسلة</t>
+        </is>
+      </c>
+      <c r="G90" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H90" s="14" t="inlineStr">
+        <is>
+          <t>حالات حدّية</t>
+        </is>
+      </c>
+      <c r="I90" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J90" s="14" t="n"/>
+      <c r="K90" s="13" t="n"/>
+      <c r="L90" s="14" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-090</t>
+        </is>
+      </c>
+      <c r="B91" s="14" t="inlineStr">
+        <is>
+          <t>الفوترة الإلكترونية (ZATCA)</t>
+        </is>
+      </c>
+      <c r="C91" s="15" t="inlineStr">
+        <is>
+          <t>إصدار متزامن بلا فجوات في ICV</t>
+        </is>
+      </c>
+      <c r="D91" s="14" t="inlineStr">
+        <is>
+          <t>عدة فواتير في اللحظة نفسها</t>
+        </is>
+      </c>
+      <c r="E91" s="14" t="inlineStr">
+        <is>
+          <t>1. اعتمد عدة دفعات/فواتير بالتوازي</t>
+        </is>
+      </c>
+      <c r="F91" s="14" t="inlineStr">
+        <is>
+          <t>ICV متصل بلا تكرار ولا فجوة، وكل فاتورة تُوقَّع مرة واحدة</t>
+        </is>
+      </c>
+      <c r="G91" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H91" s="14" t="inlineStr">
+        <is>
+          <t>حالات حدّية</t>
+        </is>
+      </c>
+      <c r="I91" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J91" s="14" t="n"/>
+      <c r="K91" s="13" t="n"/>
+      <c r="L91" s="14" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-091</t>
+        </is>
+      </c>
+      <c r="B92" s="14" t="inlineStr">
+        <is>
+          <t>الفوترة الإلكترونية (ZATCA)</t>
+        </is>
+      </c>
+      <c r="C92" s="15" t="inlineStr">
+        <is>
+          <t>فاتورة ببيانات عميل ترفضها ZATCA تُحجز حتى تُصحَّح</t>
+        </is>
+      </c>
+      <c r="D92" s="14" t="inlineStr">
+        <is>
+          <t>عميل B2B بلا عنوان وطني كامل</t>
+        </is>
+      </c>
+      <c r="E92" s="14" t="inlineStr">
+        <is>
+          <t>1. أصدر الفاتورة
+2. افتح /accounting/einvoice تبويب «فواتير موقوفة»
+3. أكمل عنوان العميل وأعد المحاولة</t>
+        </is>
+      </c>
+      <c r="F92" s="14" t="inlineStr">
+        <is>
+          <t>تُحجز الفاتورة مع سبب (einvoice_error) ولا تُشارَك ولا يُستهلك ICV؛ بعد الإصلاح تُصدَر وتُوقَّع</t>
+        </is>
+      </c>
+      <c r="G92" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H92" s="14" t="inlineStr">
+        <is>
+          <t>تحقق من المدخلات</t>
+        </is>
+      </c>
+      <c r="I92" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J92" s="14" t="n"/>
+      <c r="K92" s="13" t="n"/>
+      <c r="L92" s="14" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-092</t>
+        </is>
+      </c>
+      <c r="B93" s="14" t="inlineStr">
+        <is>
+          <t>الفوترة الإلكترونية (ZATCA)</t>
+        </is>
+      </c>
+      <c r="C93" s="15" t="inlineStr">
+        <is>
+          <t>فاتورة مبسطة B2C تُبلَّغ وتحمل الوسم 9 في QR</t>
+        </is>
+      </c>
+      <c r="D93" s="14" t="inlineStr">
+        <is>
+          <t>عميل فرد (بلا رقم ضريبي)</t>
+        </is>
+      </c>
+      <c r="E93" s="14" t="inlineStr">
+        <is>
+          <t>1. أصدر فاتورة لعميل فرد
+2. أرسلها
+3. افتح QR</t>
+        </is>
+      </c>
+      <c r="F93" s="14" t="inlineStr">
+        <is>
+          <t>النوع مبسط وتُبلَّغ (reported)، ويحوي QR الوسوم 1–9 منها 9 (توقيع الشهادة) بخلاف القياسية</t>
+        </is>
+      </c>
+      <c r="G93" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H93" s="14" t="inlineStr">
+        <is>
+          <t>تكامل</t>
+        </is>
+      </c>
+      <c r="I93" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J93" s="14" t="n"/>
+      <c r="K93" s="13" t="n"/>
+      <c r="L93" s="14" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-093</t>
+        </is>
+      </c>
+      <c r="B94" s="14" t="inlineStr">
+        <is>
+          <t>الفوترة الإلكترونية (ZATCA)</t>
+        </is>
+      </c>
+      <c r="C94" s="15" t="inlineStr">
+        <is>
+          <t>المستند الموقّع لا يتغير في قاعدة البيانات والعدّاد لا ينقص</t>
+        </is>
+      </c>
+      <c r="D94" s="14" t="inlineStr">
+        <is>
+          <t>وصول مهندس للقاعدة</t>
+        </is>
+      </c>
+      <c r="E94" s="14" t="inlineStr">
+        <is>
+          <t>1. جرّب UPDATE على XML أو الهاش لمستند موقّع
+2. جرّب DELETE
+3. جرّب تقليل icv_counter للوحدة</t>
+        </is>
+      </c>
+      <c r="F94" s="14" t="inlineStr">
+        <is>
+          <t>الكل يفشل (triggers من 0039): المستندات الموقّعة غير قابلة للتعديل ولا حذف، والعدّاد تصاعدي فقط</t>
+        </is>
+      </c>
+      <c r="G94" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H94" s="14" t="inlineStr">
+        <is>
+          <t>أمان</t>
+        </is>
+      </c>
+      <c r="I94" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J94" s="14" t="n"/>
+      <c r="K94" s="13" t="n"/>
+      <c r="L94" s="14" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-094</t>
+        </is>
+      </c>
+      <c r="B95" s="14" t="inlineStr">
+        <is>
+          <t>الفوترة الإلكترونية (ZATCA)</t>
+        </is>
+      </c>
+      <c r="C95" s="15" t="inlineStr">
+        <is>
+          <t>حزمة المراجع تحوي سجل الفواتير الإلكترونية وملفات XML</t>
+        </is>
+      </c>
+      <c r="D95" s="14" t="inlineStr">
+        <is>
+          <t>مستندات موقّعة ومعتمدة</t>
+        </is>
+      </c>
+      <c r="E95" s="14" t="inlineStr">
+        <is>
+          <t>1. حمّل حزمة المراجع
+2. افتح 19-einvoice-register وإعداد einvoice-xml</t>
+        </is>
+      </c>
+      <c r="F95" s="14" t="inlineStr">
+        <is>
+          <t>السجل يضم رقم الفاتورة وICV وUUID والحالة، وXML لكل مستند (والمعتمد منه بلاحقة -cleared)</t>
+        </is>
+      </c>
+      <c r="G95" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H95" s="14" t="inlineStr">
+        <is>
+          <t>تكامل</t>
+        </is>
+      </c>
+      <c r="I95" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J95" s="14" t="n"/>
+      <c r="K95" s="13" t="n"/>
+      <c r="L95" s="14" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-095</t>
+        </is>
+      </c>
+      <c r="B96" s="14" t="inlineStr">
+        <is>
+          <t>الفوترة الإلكترونية (ZATCA)</t>
+        </is>
+      </c>
+      <c r="C96" s="15" t="inlineStr">
+        <is>
+          <t>إيقاف التفعيل لا يوقّع مستندات جديدة</t>
+        </is>
+      </c>
+      <c r="D96" s="14" t="inlineStr">
+        <is>
+          <t>تفعيل قائم</t>
+        </is>
+      </c>
+      <c r="E96" s="14" t="inlineStr">
+        <is>
+          <t>1. أوقف «تفعيل الفوترة الإلكترونية»
+2. أصدر فاتورة</t>
+        </is>
+      </c>
+      <c r="F96" s="14" t="inlineStr">
+        <is>
+          <t>تبقى الفواتير بلا توقيع ولا يُستهلك ICV، وتبقى المستندات القديمة وحالتها كما هي</t>
+        </is>
+      </c>
+      <c r="G96" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H96" s="14" t="inlineStr">
+        <is>
+          <t>حالات حدّية</t>
+        </is>
+      </c>
+      <c r="I96" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J96" s="14" t="n"/>
+      <c r="K96" s="13" t="n"/>
+      <c r="L96" s="14" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-096</t>
+        </is>
+      </c>
+      <c r="B97" s="14" t="inlineStr">
+        <is>
+          <t>الفوترة الإلكترونية (ZATCA)</t>
+        </is>
+      </c>
+      <c r="C97" s="15" t="inlineStr">
+        <is>
+          <t>أرشيف PDF/A-3 مع XML مضمّن للفاتورة المعتمدة</t>
+        </is>
+      </c>
+      <c r="D97" s="14" t="inlineStr">
+        <is>
+          <t>فاتورة معتمدة</t>
+        </is>
+      </c>
+      <c r="E97" s="14" t="inlineStr">
+        <is>
+          <t>1. نزّل PDF الفاتورة
+2. افتح خصائص الملف</t>
+        </is>
+      </c>
+      <c r="F97" s="14" t="inlineStr">
+        <is>
+          <t>ملف PDF/A-3b يحتوي XML الفاتورة مضمّنًا كمرفق ويطابق رقم الفاتورة وUUID</t>
+        </is>
+      </c>
+      <c r="G97" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H97" s="14" t="inlineStr">
+        <is>
+          <t>تكامل</t>
+        </is>
+      </c>
+      <c r="I97" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J97" s="14" t="n"/>
+      <c r="K97" s="13" t="n"/>
+      <c r="L97" s="14" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="13" t="inlineStr">
+        <is>
+          <t>TC-E-097</t>
+        </is>
+      </c>
+      <c r="B98" s="14" t="inlineStr">
+        <is>
+          <t>الفوترة الإلكترونية (ZATCA)</t>
+        </is>
+      </c>
+      <c r="C98" s="15" t="inlineStr">
+        <is>
+          <t>مفاتيح الوحدة وشهاداتها مشفّرة في القاعدة</t>
+        </is>
+      </c>
+      <c r="D98" s="14" t="inlineStr">
+        <is>
+          <t>بيئة إنتاج</t>
+        </is>
+      </c>
+      <c r="E98" s="14" t="inlineStr">
+        <is>
+          <t>1. افتح جدول einvoice_egs
+2. اشغّل الـ API في الإنتاج بلا EINVOICE_KEY</t>
+        </is>
+      </c>
+      <c r="F98" s="14" t="inlineStr">
+        <is>
+          <t>الأعمدة المخزّنة (private_key_enc, csid_enc…) مشفّرة AES-256-GCM لا نص صريح. بدء الإنتاج بلا المفتاح يفشل برسالة واضحة</t>
+        </is>
+      </c>
+      <c r="G98" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H98" s="14" t="inlineStr">
+        <is>
+          <t>أمان</t>
+        </is>
+      </c>
+      <c r="I98" s="13" t="inlineStr">
+        <is>
+          <t>لم يُختبر</t>
+        </is>
+      </c>
+      <c r="J98" s="14" t="n"/>
+      <c r="K98" s="13" t="n"/>
+      <c r="L98" s="14" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:L98"/>
+  <conditionalFormatting sqref="A2:L98">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$I2="ناجح"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="1">
+      <formula>$I2="فاشل"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="2">
+      <formula>$I2="محجوب"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G98">
+    <cfRule type="expression" priority="4" dxfId="3">
+      <formula>$G2="P1"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation sqref="I2:I98" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"لم يُختبر,ناجح,فاشل,محجوب"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G2:G98" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"P1,P2,P3"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>